--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,19 +533,27 @@
       <c r="G2" t="n">
         <v>1610612755</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1610612753</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -594,19 +602,27 @@
       <c r="G3" t="n">
         <v>1610612766</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1610612748</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -628,7 +644,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>east_r1_1v8</t>
+          <t>east_playin_final</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -638,7 +654,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Play-In</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -646,44 +662,52 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G4" t="n">
-        <v>1610612765</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>1610612753</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J4" t="n">
+        <v>1610612766</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="N4" t="n">
         <v>1610612753</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0.6907</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1610612765</v>
-      </c>
       <c r="O4" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -703,32 +727,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G5" t="n">
         <v>1610612765</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1610612753</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -764,36 +796,44 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G6" t="n">
+        <v>1610612765</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>1610612753</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1610612765</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.4502</v>
+        <v>0.6907</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -825,32 +865,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G7" t="n">
         <v>1610612753</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>1610612765</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -886,36 +934,44 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G8" t="n">
+        <v>1610612753</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>1610612765</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Pistons</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1610612753</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.6907</v>
+        <v>0.4502</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -947,36 +1003,44 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G9" t="n">
+        <v>1610612765</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>1610612753</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1610612765</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Pistons</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.4502</v>
+        <v>0.6907</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1008,36 +1072,44 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G10" t="n">
+        <v>1610612753</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>1610612765</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Pistons</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1610612753</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Detroit Pistons</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6907</v>
+        <v>0.4502</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1055,7 +1127,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>east_r1_2v7</t>
+          <t>east_r1_1v8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1069,48 +1141,56 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>192</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1610612765</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1610612753</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0.6907</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1610612765</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1610612753</v>
+      </c>
+      <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-04-19</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>180</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1610612738</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Celtics</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1610612755</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>76ers</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>0.8048</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1610612738</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1610612755</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1130,32 +1210,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G12" t="n">
         <v>1610612738</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="J12" t="n">
         <v>1610612755</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1191,36 +1279,44 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G13" t="n">
+        <v>1610612738</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>1610612755</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>76ers</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>1610612738</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.2937</v>
+        <v>0.8048</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1252,32 +1348,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G14" t="n">
         <v>1610612755</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>1610612738</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1313,36 +1417,44 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G15" t="n">
+        <v>1610612755</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>1610612738</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Celtics</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1610612755</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.8048</v>
+        <v>0.2937</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1374,36 +1486,44 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G16" t="n">
+        <v>1610612738</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>1610612755</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>76ers</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>1610612738</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Celtics</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.2937</v>
+        <v>0.8048</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1435,36 +1555,44 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G17" t="n">
+        <v>1610612755</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>1610612738</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Celtics</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>1610612755</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.8048</v>
+        <v>0.2937</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1482,7 +1610,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>east_r1_3v6</t>
+          <t>east_r1_2v7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1496,48 +1624,56 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G18" t="n">
-        <v>1610612752</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>1610612738</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Boston Celtics</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1610612737</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>1610612755</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.6632</v>
+        <v>0.8048</v>
       </c>
       <c r="N18" t="n">
-        <v>1610612752</v>
+        <v>1610612738</v>
       </c>
       <c r="O18" t="n">
-        <v>1610612737</v>
+        <v>1610612755</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1557,32 +1693,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G19" t="n">
         <v>1610612752</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="J19" t="n">
         <v>1610612737</v>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1618,36 +1762,44 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G20" t="n">
+        <v>1610612752</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
         <v>1610612737</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Hawks</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>1610612752</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.4881</v>
+        <v>0.6632</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1679,32 +1831,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G21" t="n">
         <v>1610612737</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J21" t="n">
         <v>1610612752</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -1740,36 +1900,44 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G22" t="n">
+        <v>1610612737</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
         <v>1610612752</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Knicks</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>1610612737</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.6632</v>
+        <v>0.4881</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -1801,36 +1969,44 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G23" t="n">
+        <v>1610612752</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
         <v>1610612737</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Hawks</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>1610612752</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Knicks</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.4881</v>
+        <v>0.6632</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -1862,36 +2038,44 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G24" t="n">
+        <v>1610612737</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
         <v>1610612752</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Knicks</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>1610612737</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.6632</v>
+        <v>0.4881</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -1909,7 +2093,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>east_r1_4v5</t>
+          <t>east_r1_3v6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1923,48 +2107,56 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G25" t="n">
-        <v>1610612739</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>1610612752</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>New York Knicks</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1610612761</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
+        <v>1610612737</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.7024</v>
+        <v>0.6632</v>
       </c>
       <c r="N25" t="n">
-        <v>1610612739</v>
+        <v>1610612752</v>
       </c>
       <c r="O25" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1984,32 +2176,40 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G26" t="n">
         <v>1610612739</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="J26" t="n">
         <v>1610612761</v>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -2045,36 +2245,44 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G27" t="n">
+        <v>1610612739</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
         <v>1610612761</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Raptors</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>1610612739</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.4201</v>
+        <v>0.7024</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2106,32 +2314,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G28" t="n">
         <v>1610612761</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J28" t="n">
         <v>1610612739</v>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -2167,36 +2383,44 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G29" t="n">
+        <v>1610612761</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
         <v>1610612739</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Cavaliers</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>1610612761</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.7024</v>
+        <v>0.4201</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2228,36 +2452,44 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G30" t="n">
+        <v>1610612739</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
         <v>1610612761</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Raptors</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>1610612739</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cavaliers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.4201</v>
+        <v>0.7024</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2289,36 +2521,44 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G31" t="n">
+        <v>1610612761</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Toronto Raptors</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
         <v>1610612739</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Cavaliers</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>1610612761</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.7024</v>
+        <v>0.4201</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2336,68 +2576,76 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>west_playin_7v8</t>
+          <t>east_r1_4v5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Play-In</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="G32" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>1610612739</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
+        <v>1610612761</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.4978</v>
+        <v>0.7024</v>
       </c>
       <c r="N32" t="n">
-        <v>1610612756</v>
+        <v>1610612739</v>
       </c>
       <c r="O32" t="n">
-        <v>1610612746</v>
+        <v>1610612761</v>
       </c>
       <c r="P32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>west_playin_9v10</t>
+          <t>west_playin_7v8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,50 +2663,58 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G33" t="n">
-        <v>1610612757</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>1610612756</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1610612744</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
+        <v>1610612746</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Warriors</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.5796</v>
+        <v>0.4978</v>
       </c>
       <c r="N33" t="n">
-        <v>1610612757</v>
+        <v>1610612756</v>
       </c>
       <c r="O33" t="n">
-        <v>1610612744</v>
+        <v>1610612746</v>
       </c>
       <c r="P33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>west_r1_1v8</t>
+          <t>west_playin_9v10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2468,7 +2724,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Play-In</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2476,50 +2732,58 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G34" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>1610612757</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
+        <v>1610612744</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Golden State Warriors</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.7138</v>
+        <v>0.5796</v>
       </c>
       <c r="N34" t="n">
-        <v>1610612760</v>
+        <v>1610612757</v>
       </c>
       <c r="O34" t="n">
-        <v>1610612746</v>
+        <v>1610612744</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>west_r1_1v8</t>
+          <t>west_playin_final</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2529,52 +2793,60 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Play-In</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G35" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>1610612746</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="J35" t="n">
+        <v>1610612757</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="N35" t="n">
         <v>1610612746</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>0.7138</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1610612760</v>
-      </c>
       <c r="O35" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -2594,36 +2866,44 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G36" t="n">
+        <v>1610612760</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
         <v>1610612746</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.4175</v>
+        <v>0.7138</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2655,36 +2935,44 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G37" t="n">
+        <v>1610612760</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
         <v>1610612746</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Clippers</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>1610612760</v>
-      </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.4175</v>
+        <v>0.7138</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -2716,36 +3004,44 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G38" t="n">
+        <v>1610612746</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
         <v>1610612760</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Thunder</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>1610612746</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.7138</v>
+        <v>0.4175</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -2777,32 +3073,40 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G39" t="n">
         <v>1610612746</v>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="J39" t="n">
         <v>1610612760</v>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2838,32 +3142,40 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G40" t="n">
         <v>1610612760</v>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="J40" t="n">
         <v>1610612746</v>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2885,7 +3197,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>west_r1_2v7</t>
+          <t>west_r1_1v8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2899,54 +3211,62 @@
         </is>
       </c>
       <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>191</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1610612746</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>LA Clippers</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1610612760</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Oklahoma City Thunder</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1610612760</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1610612746</v>
+      </c>
+      <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>181</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Spurs</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
-        <v>0.7426</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2</v>
-      </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>west_r1_2v7</t>
+          <t>west_r1_1v8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2960,48 +3280,56 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G42" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>1610612760</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Oklahoma City Thunder</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
+        <v>1610612746</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7426</v>
+        <v>0.7138</v>
       </c>
       <c r="N42" t="n">
-        <v>1610612759</v>
+        <v>1610612760</v>
       </c>
       <c r="O42" t="n">
-        <v>1610612756</v>
+        <v>1610612746</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -3021,36 +3349,44 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G43" t="n">
+        <v>1610612759</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
         <v>1610612756</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.3793</v>
+        <v>0.7426</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3082,36 +3418,44 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G44" t="n">
+        <v>1610612759</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
         <v>1610612756</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Suns</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>1610612759</v>
-      </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.3793</v>
+        <v>0.7426</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3143,36 +3487,44 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G45" t="n">
+        <v>1610612756</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
         <v>1610612759</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Spurs</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>1610612756</v>
-      </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.7426</v>
+        <v>0.3793</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3204,32 +3556,40 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G46" t="n">
         <v>1610612756</v>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>1610612759</v>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3265,32 +3625,40 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G47" t="n">
         <v>1610612759</v>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Spurs</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="J47" t="n">
         <v>1610612756</v>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Suns</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -3312,7 +3680,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>west_r1_3v6</t>
+          <t>west_r1_2v7</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3326,54 +3694,62 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G48" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>1610612756</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Phoenix Suns</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1610612745</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
+        <v>1610612759</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>San Antonio Spurs</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.6656</v>
+        <v>0.3793</v>
       </c>
       <c r="N48" t="n">
-        <v>1610612747</v>
+        <v>1610612759</v>
       </c>
       <c r="O48" t="n">
-        <v>1610612745</v>
+        <v>1610612756</v>
       </c>
       <c r="P48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>west_r1_3v6</t>
+          <t>west_r1_2v7</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3387,48 +3763,56 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>193</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1610612759</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1610612756</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>PHX</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>0.7426</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1610612759</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1610612756</v>
+      </c>
+      <c r="P49" t="n">
         <v>2</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>183</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>1610612745</v>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Rockets</t>
-        </is>
-      </c>
-      <c r="M49" t="n">
-        <v>0.6656</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1610612745</v>
-      </c>
-      <c r="P49" t="n">
-        <v>3</v>
-      </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -3448,36 +3832,44 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G50" t="n">
+        <v>1610612747</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
         <v>1610612745</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Rockets</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.4505</v>
+        <v>0.6656</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3509,36 +3901,44 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G51" t="n">
+        <v>1610612747</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
         <v>1610612745</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Rockets</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>1610612747</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.4505</v>
+        <v>0.6656</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -3570,36 +3970,44 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G52" t="n">
+        <v>1610612745</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
         <v>1610612747</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Lakers</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>1610612745</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.6656</v>
+        <v>0.4505</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -3631,32 +4039,40 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G53" t="n">
         <v>1610612745</v>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>1610612747</v>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3692,32 +4108,40 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G54" t="n">
         <v>1610612747</v>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Lakers</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="J54" t="n">
         <v>1610612745</v>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Rockets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3739,7 +4163,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>west_r1_4v5</t>
+          <t>west_r1_3v6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3753,54 +4177,62 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G55" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>1610612745</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1610612750</v>
-      </c>
-      <c r="K55" t="inlineStr"/>
+        <v>1610612747</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.6589</v>
+        <v>0.4505</v>
       </c>
       <c r="N55" t="n">
-        <v>1610612743</v>
+        <v>1610612747</v>
       </c>
       <c r="O55" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="P55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>west_r1_4v5</t>
+          <t>west_r1_3v6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3814,48 +4246,56 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G56" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>1610612747</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Los Angeles Lakers</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1610612750</v>
-      </c>
-      <c r="K56" t="inlineStr"/>
+        <v>1610612745</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6589</v>
+        <v>0.6656</v>
       </c>
       <c r="N56" t="n">
-        <v>1610612743</v>
+        <v>1610612747</v>
       </c>
       <c r="O56" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="P56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -3875,36 +4315,44 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G57" t="n">
+        <v>1610612743</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
         <v>1610612750</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.4877</v>
+        <v>0.6589</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -3936,36 +4384,44 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G58" t="n">
+        <v>1610612743</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
         <v>1610612750</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Timberwolves</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>1610612743</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.4877</v>
+        <v>0.6589</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -3997,36 +4453,44 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G59" t="n">
+        <v>1610612750</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
         <v>1610612743</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Nuggets</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>1610612750</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.6589</v>
+        <v>0.4877</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4058,32 +4522,40 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G60" t="n">
         <v>1610612750</v>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="J60" t="n">
         <v>1610612743</v>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -4119,32 +4591,40 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G61" t="n">
         <v>1610612743</v>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Nuggets</t>
+          <t>Denver Nuggets</t>
         </is>
       </c>
       <c r="J61" t="n">
         <v>1610612750</v>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Timberwolves</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -4160,6 +4640,144 @@
         <v>4</v>
       </c>
       <c r="Q61" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>west_r1_4v5</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>6</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>191</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1610612750</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>1610612743</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>0.4877</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1610612743</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1610612750</v>
+      </c>
+      <c r="P62" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>west_r1_4v5</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>193</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1610612743</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1610612750</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>0.6589</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1610612743</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1610612750</v>
+      </c>
+      <c r="P63" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q63" t="n">
         <v>5</v>
       </c>
     </row>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -544,26 +544,26 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4839</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
       </c>
       <c r="O2" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -613,26 +613,26 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.6569</v>
+        <v>0.6994</v>
       </c>
       <c r="N3" t="n">
         <v>1610612766</v>
       </c>
       <c r="O3" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -669,16 +669,16 @@
         <v>178</v>
       </c>
       <c r="G4" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4321</v>
+        <v>0.4989</v>
       </c>
       <c r="N4" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="O4" t="n">
         <v>1610612766</v>
@@ -751,26 +751,26 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.6907</v>
+        <v>0.629</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
       </c>
       <c r="O5" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -820,26 +820,26 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6907</v>
+        <v>0.629</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
       </c>
       <c r="O6" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -876,16 +876,16 @@
         <v>184</v>
       </c>
       <c r="G7" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.4502</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
       </c>
       <c r="O7" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -945,16 +945,16 @@
         <v>186</v>
       </c>
       <c r="G8" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.4502</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
       </c>
       <c r="O8" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1027,26 +1027,26 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6907</v>
+        <v>0.629</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
       </c>
       <c r="O9" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1083,16 +1083,16 @@
         <v>190</v>
       </c>
       <c r="G10" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.4502</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
       </c>
       <c r="O10" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1165,26 +1165,26 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6907</v>
+        <v>0.629</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
       </c>
       <c r="O11" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.8048</v>
+        <v>0.7862</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.8048</v>
+        <v>0.7862</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.2937</v>
+        <v>0.3154</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.2937</v>
+        <v>0.3154</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.8048</v>
+        <v>0.7862</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.2937</v>
+        <v>0.3154</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.8048</v>
+        <v>0.7862</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7024</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7024</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4201</v>
+        <v>0.4113</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4201</v>
+        <v>0.4113</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7024</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4201</v>
+        <v>0.4113</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7024</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4978</v>
+        <v>0.4959</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6891</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6656</v>
+        <v>0.654</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6656</v>
+        <v>0.654</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4505</v>
+        <v>0.4659</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4505</v>
+        <v>0.4659</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6656</v>
+        <v>0.654</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4505</v>
+        <v>0.4659</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6656</v>
+        <v>0.654</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6589</v>
+        <v>0.6577</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6589</v>
+        <v>0.6577</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4877</v>
+        <v>0.489</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4877</v>
+        <v>0.489</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6589</v>
+        <v>0.6577</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4877</v>
+        <v>0.489</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6589</v>
+        <v>0.6577</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.4839</v>
+        <v>0.4932</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.6994</v>
+        <v>0.7027</v>
       </c>
       <c r="N3" t="n">
         <v>1610612766</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.629</v>
+        <v>0.6712</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.629</v>
+        <v>0.6712</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.629</v>
+        <v>0.6712</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.515</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.629</v>
+        <v>0.6712</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3154</v>
+        <v>0.2964</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3154</v>
+        <v>0.2964</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3154</v>
+        <v>0.2964</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1717,26 +1717,26 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6632</v>
+        <v>0.736</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
       </c>
       <c r="O19" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6632</v>
+        <v>0.736</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
       </c>
       <c r="O20" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
@@ -1842,16 +1842,16 @@
         <v>184</v>
       </c>
       <c r="G21" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4881</v>
+        <v>0.4156</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
       </c>
       <c r="O21" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P21" t="n">
         <v>3</v>
@@ -1911,16 +1911,16 @@
         <v>186</v>
       </c>
       <c r="G22" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4881</v>
+        <v>0.4156</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
       </c>
       <c r="O22" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -1993,26 +1993,26 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.6632</v>
+        <v>0.736</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
       </c>
       <c r="O23" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -2049,16 +2049,16 @@
         <v>190</v>
       </c>
       <c r="G24" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4881</v>
+        <v>0.4156</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
       </c>
       <c r="O24" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
@@ -2131,26 +2131,26 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.6632</v>
+        <v>0.736</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
       </c>
       <c r="O25" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
@@ -2200,26 +2200,26 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.663</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
       </c>
       <c r="O26" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P26" t="n">
         <v>4</v>
@@ -2269,26 +2269,26 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.663</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
       </c>
       <c r="O27" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P27" t="n">
         <v>4</v>
@@ -2325,16 +2325,16 @@
         <v>184</v>
       </c>
       <c r="G28" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2351,13 +2351,13 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4113</v>
+        <v>0.5008</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
       </c>
       <c r="O28" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P28" t="n">
         <v>4</v>
@@ -2394,16 +2394,16 @@
         <v>186</v>
       </c>
       <c r="G29" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2420,13 +2420,13 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4113</v>
+        <v>0.5008</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
       </c>
       <c r="O29" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P29" t="n">
         <v>4</v>
@@ -2476,26 +2476,26 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.663</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
       </c>
       <c r="O30" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P30" t="n">
         <v>4</v>
@@ -2532,16 +2532,16 @@
         <v>190</v>
       </c>
       <c r="G31" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4113</v>
+        <v>0.5008</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
       </c>
       <c r="O31" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P31" t="n">
         <v>4</v>
@@ -2614,26 +2614,26 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.663</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
       </c>
       <c r="O32" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P32" t="n">
         <v>4</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4959</v>
+        <v>0.4778</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5796</v>
+        <v>0.5934</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7138</v>
+        <v>0.7509</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7138</v>
+        <v>0.7509</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7138</v>
+        <v>0.7509</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7138</v>
+        <v>0.7509</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7426</v>
+        <v>0.7571</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7426</v>
+        <v>0.7571</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7426</v>
+        <v>0.7571</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7426</v>
+        <v>0.7571</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.654</v>
+        <v>0.6697</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.654</v>
+        <v>0.6697</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.654</v>
+        <v>0.6697</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.654</v>
+        <v>0.6697</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6577</v>
+        <v>0.6445</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6577</v>
+        <v>0.6445</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.489</v>
+        <v>0.4951</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.489</v>
+        <v>0.4951</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6577</v>
+        <v>0.6445</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.489</v>
+        <v>0.4951</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6577</v>
+        <v>0.6445</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.4932</v>
+        <v>0.4977</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.7027</v>
+        <v>0.7015</v>
       </c>
       <c r="N3" t="n">
         <v>1610612766</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.6712</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6712</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.515</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.515</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6712</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.515</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6712</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7862</v>
+        <v>0.784</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7862</v>
+        <v>0.784</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.2964</v>
+        <v>0.2983</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.2964</v>
+        <v>0.2983</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7862</v>
+        <v>0.784</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.2964</v>
+        <v>0.2983</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7862</v>
+        <v>0.784</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.736</v>
+        <v>0.726</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.736</v>
+        <v>0.726</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4156</v>
+        <v>0.4285</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4156</v>
+        <v>0.4285</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.736</v>
+        <v>0.726</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4156</v>
+        <v>0.4285</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.736</v>
+        <v>0.726</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.663</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.663</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.5008</v>
+        <v>0.4935</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.5008</v>
+        <v>0.4935</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.663</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.5008</v>
+        <v>0.4935</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.663</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4778</v>
+        <v>0.4711</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.6891</v>
+        <v>0.699</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7509</v>
+        <v>0.736</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7509</v>
+        <v>0.736</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.4175</v>
+        <v>0.4227</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.4175</v>
+        <v>0.4227</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7509</v>
+        <v>0.736</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.4175</v>
+        <v>0.4227</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7509</v>
+        <v>0.736</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7571</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7571</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3793</v>
+        <v>0.3345</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3793</v>
+        <v>0.3345</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7571</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3793</v>
+        <v>0.3345</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7571</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4659</v>
+        <v>0.4398</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4659</v>
+        <v>0.4398</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4659</v>
+        <v>0.4398</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6445</v>
+        <v>0.6577</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6445</v>
+        <v>0.6577</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4951</v>
+        <v>0.4483</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4951</v>
+        <v>0.4483</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6445</v>
+        <v>0.6577</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4951</v>
+        <v>0.4483</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6445</v>
+        <v>0.6577</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -544,26 +544,26 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.4977</v>
+        <v>0.5578</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
       </c>
       <c r="O2" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -613,26 +613,26 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.7015</v>
+        <v>0.6143</v>
       </c>
       <c r="N3" t="n">
         <v>1610612766</v>
       </c>
       <c r="O3" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -669,16 +669,16 @@
         <v>178</v>
       </c>
       <c r="G4" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4989</v>
+        <v>0.4439</v>
       </c>
       <c r="N4" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="O4" t="n">
         <v>1610612766</v>
@@ -751,26 +751,26 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
       </c>
       <c r="O5" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -820,26 +820,26 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
       </c>
       <c r="O6" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -876,16 +876,16 @@
         <v>184</v>
       </c>
       <c r="G7" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4277</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
       </c>
       <c r="O7" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -945,16 +945,16 @@
         <v>186</v>
       </c>
       <c r="G8" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4277</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
       </c>
       <c r="O8" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1027,26 +1027,26 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
       </c>
       <c r="O9" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1083,16 +1083,16 @@
         <v>190</v>
       </c>
       <c r="G10" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4277</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
       </c>
       <c r="O10" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1165,26 +1165,26 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
       </c>
       <c r="O11" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.784</v>
+        <v>0.7687</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.784</v>
+        <v>0.7687</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.2983</v>
+        <v>0.3097</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.2983</v>
+        <v>0.3097</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.784</v>
+        <v>0.7687</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.2983</v>
+        <v>0.3097</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.784</v>
+        <v>0.7687</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.726</v>
+        <v>0.7398</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.726</v>
+        <v>0.7398</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4285</v>
+        <v>0.413</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4285</v>
+        <v>0.413</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.726</v>
+        <v>0.7398</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4285</v>
+        <v>0.413</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.726</v>
+        <v>0.7398</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6752</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6752</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4935</v>
+        <v>0.4912</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4935</v>
+        <v>0.4912</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6752</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4935</v>
+        <v>0.4912</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6752</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4711</v>
+        <v>0.451</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5934</v>
+        <v>0.6049</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.699</v>
+        <v>0.7047</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.736</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.736</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.4227</v>
+        <v>0.4432</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.4227</v>
+        <v>0.4432</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.736</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.4227</v>
+        <v>0.4432</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.736</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7886</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7886</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3345</v>
+        <v>0.3213</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3345</v>
+        <v>0.3213</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7886</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3345</v>
+        <v>0.3213</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7886</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6697</v>
+        <v>0.6701</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6697</v>
+        <v>0.6701</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4398</v>
+        <v>0.4397</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4398</v>
+        <v>0.4397</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6697</v>
+        <v>0.6701</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4398</v>
+        <v>0.4397</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6697</v>
+        <v>0.6701</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6577</v>
+        <v>0.6632</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6577</v>
+        <v>0.6632</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4483</v>
+        <v>0.4636</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4483</v>
+        <v>0.4636</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6577</v>
+        <v>0.6632</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4483</v>
+        <v>0.4636</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6577</v>
+        <v>0.6632</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -544,26 +544,26 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.5578</v>
+        <v>0.3996</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
       </c>
       <c r="O2" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -600,16 +600,16 @@
         <v>176</v>
       </c>
       <c r="G3" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.6143</v>
+        <v>0.5049</v>
       </c>
       <c r="N3" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="O3" t="n">
         <v>1610612748</v>
@@ -669,39 +669,39 @@
         <v>178</v>
       </c>
       <c r="G4" t="n">
+        <v>1610612766</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>1610612753</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>ORL</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
+        <v>0.6939</v>
+      </c>
+      <c r="N4" t="n">
         <v>1610612766</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>CHA</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0.4439</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1610612753</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1610612766</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -751,26 +751,26 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.6202</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
       </c>
       <c r="O5" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -820,26 +820,26 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.6202</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
       </c>
       <c r="O6" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -876,16 +876,16 @@
         <v>184</v>
       </c>
       <c r="G7" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.4277</v>
+        <v>0.5411</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
       </c>
       <c r="O7" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -945,16 +945,16 @@
         <v>186</v>
       </c>
       <c r="G8" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.4277</v>
+        <v>0.5411</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
       </c>
       <c r="O8" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1027,26 +1027,26 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.6202</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
       </c>
       <c r="O9" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1083,16 +1083,16 @@
         <v>190</v>
       </c>
       <c r="G10" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.4277</v>
+        <v>0.5411</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
       </c>
       <c r="O10" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1165,26 +1165,26 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.6202</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
       </c>
       <c r="O11" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3097</v>
+        <v>0.3123</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3097</v>
+        <v>0.3123</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3097</v>
+        <v>0.3123</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1717,26 +1717,26 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7398</v>
+        <v>0.658</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
       </c>
       <c r="O19" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7398</v>
+        <v>0.658</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
       </c>
       <c r="O20" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
@@ -1842,16 +1842,16 @@
         <v>184</v>
       </c>
       <c r="G21" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.413</v>
+        <v>0.496</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
       </c>
       <c r="O21" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P21" t="n">
         <v>3</v>
@@ -1911,16 +1911,16 @@
         <v>186</v>
       </c>
       <c r="G22" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.413</v>
+        <v>0.496</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
       </c>
       <c r="O22" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -1993,26 +1993,26 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.7398</v>
+        <v>0.658</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
       </c>
       <c r="O23" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -2049,16 +2049,16 @@
         <v>190</v>
       </c>
       <c r="G24" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.413</v>
+        <v>0.496</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
       </c>
       <c r="O24" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
@@ -2131,26 +2131,26 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.7398</v>
+        <v>0.658</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
       </c>
       <c r="O25" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
@@ -2200,26 +2200,26 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.6752</v>
+        <v>0.7224</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
       </c>
       <c r="O26" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P26" t="n">
         <v>4</v>
@@ -2269,26 +2269,26 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.6752</v>
+        <v>0.7224</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
       </c>
       <c r="O27" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P27" t="n">
         <v>4</v>
@@ -2325,16 +2325,16 @@
         <v>184</v>
       </c>
       <c r="G28" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2351,13 +2351,13 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4912</v>
+        <v>0.3678</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
       </c>
       <c r="O28" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P28" t="n">
         <v>4</v>
@@ -2394,16 +2394,16 @@
         <v>186</v>
       </c>
       <c r="G29" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2420,13 +2420,13 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4912</v>
+        <v>0.3678</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
       </c>
       <c r="O29" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P29" t="n">
         <v>4</v>
@@ -2476,26 +2476,26 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.6752</v>
+        <v>0.7224</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
       </c>
       <c r="O30" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P30" t="n">
         <v>4</v>
@@ -2532,16 +2532,16 @@
         <v>190</v>
       </c>
       <c r="G31" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4912</v>
+        <v>0.3678</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
       </c>
       <c r="O31" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P31" t="n">
         <v>4</v>
@@ -2614,26 +2614,26 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.6752</v>
+        <v>0.7224</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
       </c>
       <c r="O32" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P32" t="n">
         <v>4</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.6049</v>
+        <v>0.6112</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.7351</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.7351</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.4432</v>
+        <v>0.4374</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.4432</v>
+        <v>0.4374</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.7351</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.4432</v>
+        <v>0.4374</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.7351</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7886</v>
+        <v>0.7853</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7886</v>
+        <v>0.7853</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3213</v>
+        <v>0.3248</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3213</v>
+        <v>0.3248</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7886</v>
+        <v>0.7853</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3213</v>
+        <v>0.3248</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7886</v>
+        <v>0.7853</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4397</v>
+        <v>0.452</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4397</v>
+        <v>0.452</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4397</v>
+        <v>0.452</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6632</v>
+        <v>0.6644</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6632</v>
+        <v>0.6644</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4636</v>
+        <v>0.4516</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4636</v>
+        <v>0.4516</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6632</v>
+        <v>0.6644</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4636</v>
+        <v>0.4516</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6632</v>
+        <v>0.6644</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.3996</v>
+        <v>0.4002</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.5049</v>
+        <v>0.5244</v>
       </c>
       <c r="N3" t="n">
         <v>1610612753</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.6939</v>
+        <v>0.6921</v>
       </c>
       <c r="N4" t="n">
         <v>1610612766</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7687</v>
+        <v>0.7825</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7687</v>
+        <v>0.7825</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3123</v>
+        <v>0.3165</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3123</v>
+        <v>0.3165</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7687</v>
+        <v>0.7825</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3123</v>
+        <v>0.3165</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7687</v>
+        <v>0.7825</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.658</v>
+        <v>0.6671</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.658</v>
+        <v>0.6671</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.496</v>
+        <v>0.494</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.496</v>
+        <v>0.494</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.658</v>
+        <v>0.6671</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.496</v>
+        <v>0.494</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.658</v>
+        <v>0.6671</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7224</v>
+        <v>0.7249</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7224</v>
+        <v>0.7249</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.3678</v>
+        <v>0.3588</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.3678</v>
+        <v>0.3588</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7224</v>
+        <v>0.7249</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.3678</v>
+        <v>0.3588</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7224</v>
+        <v>0.7249</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.451</v>
+        <v>0.4592</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.6112</v>
+        <v>0.5655</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.7047</v>
+        <v>0.7117</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7351</v>
+        <v>0.7363</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7351</v>
+        <v>0.7363</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.4374</v>
+        <v>0.423</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.4374</v>
+        <v>0.423</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7351</v>
+        <v>0.7363</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.4374</v>
+        <v>0.423</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7351</v>
+        <v>0.7363</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7853</v>
+        <v>0.7835</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7853</v>
+        <v>0.7835</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3248</v>
+        <v>0.3293</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3248</v>
+        <v>0.3293</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7853</v>
+        <v>0.7835</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3248</v>
+        <v>0.3293</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7853</v>
+        <v>0.7835</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6701</v>
+        <v>0.6806</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6701</v>
+        <v>0.6806</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.452</v>
+        <v>0.4248</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.452</v>
+        <v>0.4248</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6701</v>
+        <v>0.6806</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.452</v>
+        <v>0.4248</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6701</v>
+        <v>0.6806</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6644</v>
+        <v>0.6943</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6644</v>
+        <v>0.6943</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4516</v>
+        <v>0.4038</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4516</v>
+        <v>0.4038</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6644</v>
+        <v>0.6943</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4516</v>
+        <v>0.4038</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6644</v>
+        <v>0.6943</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.4002</v>
+        <v>0.4358</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.5244</v>
+        <v>0.499</v>
       </c>
       <c r="N3" t="n">
         <v>1610612753</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.6921</v>
+        <v>0.6802</v>
       </c>
       <c r="N4" t="n">
         <v>1610612766</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.6202</v>
+        <v>0.591</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6202</v>
+        <v>0.591</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.5411</v>
+        <v>0.5002</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.5411</v>
+        <v>0.5002</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6202</v>
+        <v>0.591</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.5411</v>
+        <v>0.5002</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6202</v>
+        <v>0.591</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7825</v>
+        <v>0.7867</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7825</v>
+        <v>0.7867</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3165</v>
+        <v>0.3284</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3165</v>
+        <v>0.3284</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7825</v>
+        <v>0.7867</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3165</v>
+        <v>0.3284</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7825</v>
+        <v>0.7867</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6671</v>
+        <v>0.6624</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6671</v>
+        <v>0.6624</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.494</v>
+        <v>0.4617</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.494</v>
+        <v>0.4617</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.6671</v>
+        <v>0.6624</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.494</v>
+        <v>0.4617</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.6671</v>
+        <v>0.6624</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7249</v>
+        <v>0.7331</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7249</v>
+        <v>0.7331</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.3588</v>
+        <v>0.4034</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.3588</v>
+        <v>0.4034</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7249</v>
+        <v>0.7331</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.3588</v>
+        <v>0.4034</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7249</v>
+        <v>0.7331</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4592</v>
+        <v>0.4697</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5655</v>
+        <v>0.5612</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.7117</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7363</v>
+        <v>0.6996</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7363</v>
+        <v>0.6996</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.423</v>
+        <v>0.3704</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.423</v>
+        <v>0.3704</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7363</v>
+        <v>0.6996</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.423</v>
+        <v>0.3704</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7363</v>
+        <v>0.6996</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7835</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7835</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3293</v>
+        <v>0.3365</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3293</v>
+        <v>0.3365</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7835</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3293</v>
+        <v>0.3365</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7835</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6806</v>
+        <v>0.6926</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6806</v>
+        <v>0.6926</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4248</v>
+        <v>0.4686</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4248</v>
+        <v>0.4686</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6806</v>
+        <v>0.6926</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4248</v>
+        <v>0.4686</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6806</v>
+        <v>0.6926</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6943</v>
+        <v>0.7057</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6943</v>
+        <v>0.7057</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4038</v>
+        <v>0.4234</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4038</v>
+        <v>0.4234</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6943</v>
+        <v>0.7057</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4038</v>
+        <v>0.4234</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6943</v>
+        <v>0.7057</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -544,26 +544,26 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.4358</v>
+        <v>0.5982</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
       </c>
       <c r="O2" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -600,39 +600,39 @@
         <v>176</v>
       </c>
       <c r="G3" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="J3" t="n">
+        <v>1610612766</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5204</v>
+      </c>
+      <c r="N3" t="n">
         <v>1610612748</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1610612753</v>
-      </c>
       <c r="O3" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -669,39 +669,39 @@
         <v>178</v>
       </c>
       <c r="G4" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J4" t="n">
+        <v>1610612748</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5044</v>
+      </c>
+      <c r="N4" t="n">
         <v>1610612753</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ORL</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Orlando Magic</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0.6802</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1610612766</v>
-      </c>
       <c r="O4" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -751,26 +751,26 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.591</v>
+        <v>0.7108</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
       </c>
       <c r="O5" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -820,26 +820,26 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.591</v>
+        <v>0.7108</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
       </c>
       <c r="O6" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -876,16 +876,16 @@
         <v>184</v>
       </c>
       <c r="G7" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.5002</v>
+        <v>0.3813</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
       </c>
       <c r="O7" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -945,16 +945,16 @@
         <v>186</v>
       </c>
       <c r="G8" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.5002</v>
+        <v>0.3813</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
       </c>
       <c r="O8" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1027,26 +1027,26 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.591</v>
+        <v>0.7108</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
       </c>
       <c r="O9" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1083,16 +1083,16 @@
         <v>190</v>
       </c>
       <c r="G10" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.5002</v>
+        <v>0.3813</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
       </c>
       <c r="O10" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1165,26 +1165,26 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Orlando Magic</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.591</v>
+        <v>0.7108</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
       </c>
       <c r="O11" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7867</v>
+        <v>0.726</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7867</v>
+        <v>0.726</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3284</v>
+        <v>0.3628</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3284</v>
+        <v>0.3628</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7867</v>
+        <v>0.726</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3284</v>
+        <v>0.3628</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7867</v>
+        <v>0.726</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6624</v>
+        <v>0.6583</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6624</v>
+        <v>0.6583</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4617</v>
+        <v>0.4702</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4617</v>
+        <v>0.4702</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.6624</v>
+        <v>0.6583</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4617</v>
+        <v>0.4702</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.6624</v>
+        <v>0.6583</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7331</v>
+        <v>0.7322</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7331</v>
+        <v>0.7322</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4034</v>
+        <v>0.4065</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4034</v>
+        <v>0.4065</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7331</v>
+        <v>0.7322</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4034</v>
+        <v>0.4065</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7331</v>
+        <v>0.7322</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4697</v>
+        <v>0.4746</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5612</v>
+        <v>0.5669</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7191</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.3704</v>
+        <v>0.3742</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.3704</v>
+        <v>0.3742</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.3704</v>
+        <v>0.3742</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7733</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7733</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3365</v>
+        <v>0.3417</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3365</v>
+        <v>0.3417</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7733</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3365</v>
+        <v>0.3417</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7733</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6926</v>
+        <v>0.6933</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6926</v>
+        <v>0.6933</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4686</v>
+        <v>0.4731</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4686</v>
+        <v>0.4731</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6926</v>
+        <v>0.6933</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4686</v>
+        <v>0.4731</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6926</v>
+        <v>0.6933</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.7057</v>
+        <v>0.7089</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.7057</v>
+        <v>0.7089</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4234</v>
+        <v>0.4433</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4234</v>
+        <v>0.4433</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.7057</v>
+        <v>0.7089</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4234</v>
+        <v>0.4433</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.7057</v>
+        <v>0.7089</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.5982</v>
+        <v>0.604</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.5204</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>1610612748</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.5044</v>
+        <v>0.5034</v>
       </c>
       <c r="N4" t="n">
         <v>1610612753</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7108</v>
+        <v>0.7129</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7108</v>
+        <v>0.7129</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.3813</v>
+        <v>0.3809</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.3813</v>
+        <v>0.3809</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.7108</v>
+        <v>0.7129</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.3813</v>
+        <v>0.3809</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7108</v>
+        <v>0.7129</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.726</v>
+        <v>0.7111</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.726</v>
+        <v>0.7111</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3628</v>
+        <v>0.3781</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3628</v>
+        <v>0.3781</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.726</v>
+        <v>0.7111</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3628</v>
+        <v>0.3781</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.726</v>
+        <v>0.7111</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6583</v>
+        <v>0.6803</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6583</v>
+        <v>0.6803</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4702</v>
+        <v>0.4442</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4702</v>
+        <v>0.4442</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.6583</v>
+        <v>0.6803</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4702</v>
+        <v>0.4442</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.6583</v>
+        <v>0.6803</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4065</v>
+        <v>0.4086</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4065</v>
+        <v>0.4086</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4065</v>
+        <v>0.4086</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4746</v>
+        <v>0.4965</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.7191</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.6996</v>
+        <v>0.7498</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.6996</v>
+        <v>0.7498</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.3742</v>
+        <v>0.3528</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.3742</v>
+        <v>0.3528</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.6996</v>
+        <v>0.7498</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.3742</v>
+        <v>0.3528</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.6996</v>
+        <v>0.7498</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7733</v>
+        <v>0.7811</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7733</v>
+        <v>0.7811</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3417</v>
+        <v>0.334</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3417</v>
+        <v>0.334</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7733</v>
+        <v>0.7811</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3417</v>
+        <v>0.334</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7733</v>
+        <v>0.7811</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6933</v>
+        <v>0.6955</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6933</v>
+        <v>0.6955</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4731</v>
+        <v>0.4605</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4731</v>
+        <v>0.4605</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6933</v>
+        <v>0.6955</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4731</v>
+        <v>0.4605</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6933</v>
+        <v>0.6955</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.7089</v>
+        <v>0.7138</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.7089</v>
+        <v>0.7138</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4433</v>
+        <v>0.4421</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4433</v>
+        <v>0.4421</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.7089</v>
+        <v>0.7138</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4433</v>
+        <v>0.4421</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.7089</v>
+        <v>0.7138</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.604</v>
+        <v>0.6102</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -600,39 +600,39 @@
         <v>176</v>
       </c>
       <c r="G3" t="n">
+        <v>1610612766</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>1610612748</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
+        <v>0.6397</v>
+      </c>
+      <c r="N3" t="n">
         <v>1610612766</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>CHA</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0.5145999999999999</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1610612748</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1610612766</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -682,26 +682,26 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Miami Heat</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.5034</v>
+        <v>0.4507</v>
       </c>
       <c r="N4" t="n">
         <v>1610612753</v>
       </c>
       <c r="O4" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7129</v>
+        <v>0.7229</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7129</v>
+        <v>0.7229</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.3809</v>
+        <v>0.3883</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.3809</v>
+        <v>0.3883</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.7129</v>
+        <v>0.7229</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.3809</v>
+        <v>0.3883</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7129</v>
+        <v>0.7229</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7111</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7111</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3781</v>
+        <v>0.4099</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3781</v>
+        <v>0.4099</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7111</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3781</v>
+        <v>0.4099</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7111</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6803</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6803</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4442</v>
+        <v>0.4404</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4442</v>
+        <v>0.4404</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.6803</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4442</v>
+        <v>0.4404</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.6803</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7322</v>
+        <v>0.7271</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7322</v>
+        <v>0.7271</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4086</v>
+        <v>0.4274</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4086</v>
+        <v>0.4274</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7322</v>
+        <v>0.7271</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4086</v>
+        <v>0.4274</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7322</v>
+        <v>0.7271</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4965</v>
+        <v>0.5068</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5669</v>
+        <v>0.5887</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6882</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7498</v>
+        <v>0.7574</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7498</v>
+        <v>0.7574</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.3528</v>
+        <v>0.3617</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.3528</v>
+        <v>0.3617</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7498</v>
+        <v>0.7574</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.3528</v>
+        <v>0.3617</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7498</v>
+        <v>0.7574</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7811</v>
+        <v>0.7837</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7811</v>
+        <v>0.7837</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.334</v>
+        <v>0.3367</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.334</v>
+        <v>0.3367</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7811</v>
+        <v>0.7837</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.334</v>
+        <v>0.3367</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7811</v>
+        <v>0.7837</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6955</v>
+        <v>0.6806</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6955</v>
+        <v>0.6806</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4605</v>
+        <v>0.4612</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4605</v>
+        <v>0.4612</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6955</v>
+        <v>0.6806</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4605</v>
+        <v>0.4612</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6955</v>
+        <v>0.6806</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.7138</v>
+        <v>0.6979</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.7138</v>
+        <v>0.6979</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4421</v>
+        <v>0.4499</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4421</v>
+        <v>0.4499</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.7138</v>
+        <v>0.6979</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4421</v>
+        <v>0.4499</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.7138</v>
+        <v>0.6979</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.6102</v>
+        <v>0.6342</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -600,39 +600,39 @@
         <v>176</v>
       </c>
       <c r="G3" t="n">
+        <v>1610612748</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>1610612766</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>CHA</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Charlotte Hornets</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="N3" t="n">
         <v>1610612748</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0.6397</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1610612766</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1610612748</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -682,26 +682,26 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Charlotte Hornets</t>
+          <t>Miami Heat</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4507</v>
+        <v>0.4851</v>
       </c>
       <c r="N4" t="n">
         <v>1610612753</v>
       </c>
       <c r="O4" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7229</v>
+        <v>0.7133</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7229</v>
+        <v>0.7133</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.3883</v>
+        <v>0.4287</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.3883</v>
+        <v>0.4287</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.7229</v>
+        <v>0.7133</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.3883</v>
+        <v>0.4287</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7229</v>
+        <v>0.7133</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.4099</v>
+        <v>0.3697</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.4099</v>
+        <v>0.3697</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.4099</v>
+        <v>0.3697</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6558</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6558</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4404</v>
+        <v>0.457</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4404</v>
+        <v>0.457</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6558</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4404</v>
+        <v>0.457</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6558</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7271</v>
+        <v>0.6946</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7271</v>
+        <v>0.6946</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4274</v>
+        <v>0.4538</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4274</v>
+        <v>0.4538</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7271</v>
+        <v>0.6946</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4274</v>
+        <v>0.4538</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7271</v>
+        <v>0.6946</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.5068</v>
+        <v>0.5026</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5887</v>
+        <v>0.578</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.6882</v>
+        <v>0.7236</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7574</v>
+        <v>0.6933</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7574</v>
+        <v>0.6933</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.3617</v>
+        <v>0.3836</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.3617</v>
+        <v>0.3836</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7574</v>
+        <v>0.6933</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.3617</v>
+        <v>0.3836</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7574</v>
+        <v>0.6933</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7837</v>
+        <v>0.7876</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7837</v>
+        <v>0.7876</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3367</v>
+        <v>0.3338</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3367</v>
+        <v>0.3338</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7837</v>
+        <v>0.7876</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3367</v>
+        <v>0.3338</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7837</v>
+        <v>0.7876</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6806</v>
+        <v>0.6661</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6806</v>
+        <v>0.6661</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4612</v>
+        <v>0.4683</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4612</v>
+        <v>0.4683</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6806</v>
+        <v>0.6661</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4612</v>
+        <v>0.4683</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6806</v>
+        <v>0.6661</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6979</v>
+        <v>0.7214</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6979</v>
+        <v>0.7214</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4499</v>
+        <v>0.4413</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4499</v>
+        <v>0.4413</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6979</v>
+        <v>0.7214</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4499</v>
+        <v>0.4413</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6979</v>
+        <v>0.7214</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.6342</v>
+        <v>0.6089</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.4994</v>
+        <v>0.4714</v>
       </c>
       <c r="N3" t="n">
         <v>1610612748</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4851</v>
+        <v>0.5153</v>
       </c>
       <c r="N4" t="n">
         <v>1610612753</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7133</v>
+        <v>0.7155</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7133</v>
+        <v>0.7155</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.4287</v>
+        <v>0.4253</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.4287</v>
+        <v>0.4253</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.7133</v>
+        <v>0.7155</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.4287</v>
+        <v>0.4253</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133</v>
+        <v>0.7155</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.715</v>
+        <v>0.7544</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.715</v>
+        <v>0.7544</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3697</v>
+        <v>0.3548</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3697</v>
+        <v>0.3548</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.715</v>
+        <v>0.7544</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3697</v>
+        <v>0.3548</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.715</v>
+        <v>0.7544</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1717,26 +1717,26 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6558</v>
+        <v>0.725</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
       </c>
       <c r="O19" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6558</v>
+        <v>0.725</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
       </c>
       <c r="O20" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
@@ -1842,16 +1842,16 @@
         <v>184</v>
       </c>
       <c r="G21" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.457</v>
+        <v>0.4</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
       </c>
       <c r="O21" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P21" t="n">
         <v>3</v>
@@ -1911,16 +1911,16 @@
         <v>186</v>
       </c>
       <c r="G22" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.457</v>
+        <v>0.4</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
       </c>
       <c r="O22" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -1993,26 +1993,26 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.6558</v>
+        <v>0.725</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
       </c>
       <c r="O23" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -2049,16 +2049,16 @@
         <v>190</v>
       </c>
       <c r="G24" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.457</v>
+        <v>0.4</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
       </c>
       <c r="O24" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
@@ -2131,26 +2131,26 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Atlanta Hawks</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.6558</v>
+        <v>0.725</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
       </c>
       <c r="O25" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
@@ -2200,26 +2200,26 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.6946</v>
+        <v>0.6866</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
       </c>
       <c r="O26" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P26" t="n">
         <v>4</v>
@@ -2269,26 +2269,26 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.6946</v>
+        <v>0.6866</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
       </c>
       <c r="O27" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P27" t="n">
         <v>4</v>
@@ -2325,16 +2325,16 @@
         <v>184</v>
       </c>
       <c r="G28" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2351,13 +2351,13 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4538</v>
+        <v>0.4476</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
       </c>
       <c r="O28" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P28" t="n">
         <v>4</v>
@@ -2394,16 +2394,16 @@
         <v>186</v>
       </c>
       <c r="G29" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2420,13 +2420,13 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4538</v>
+        <v>0.4476</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
       </c>
       <c r="O29" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P29" t="n">
         <v>4</v>
@@ -2476,26 +2476,26 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.6946</v>
+        <v>0.6866</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
       </c>
       <c r="O30" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P30" t="n">
         <v>4</v>
@@ -2532,16 +2532,16 @@
         <v>190</v>
       </c>
       <c r="G31" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4538</v>
+        <v>0.4476</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
       </c>
       <c r="O31" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P31" t="n">
         <v>4</v>
@@ -2614,26 +2614,26 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Atlanta Hawks</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.6946</v>
+        <v>0.6866</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
       </c>
       <c r="O32" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P32" t="n">
         <v>4</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.5026</v>
+        <v>0.4879</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.578</v>
+        <v>0.5969</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.7236</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.6933</v>
+        <v>0.7319</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.6933</v>
+        <v>0.7319</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.3836</v>
+        <v>0.3788</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.3836</v>
+        <v>0.3788</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.6933</v>
+        <v>0.7319</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.3836</v>
+        <v>0.3788</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.6933</v>
+        <v>0.7319</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7876</v>
+        <v>0.7869</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7876</v>
+        <v>0.7869</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3338</v>
+        <v>0.3246</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3338</v>
+        <v>0.3246</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7876</v>
+        <v>0.7869</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3338</v>
+        <v>0.3246</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7876</v>
+        <v>0.7869</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6661</v>
+        <v>0.6407</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6661</v>
+        <v>0.6407</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4683</v>
+        <v>0.5299</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4683</v>
+        <v>0.5299</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6661</v>
+        <v>0.6407</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4683</v>
+        <v>0.5299</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6661</v>
+        <v>0.6407</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.7214</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.7214</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4413</v>
+        <v>0.4843</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4413</v>
+        <v>0.4843</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.7214</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4413</v>
+        <v>0.4843</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.7214</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.6089</v>
+        <v>0.6029</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.4714</v>
+        <v>0.4934</v>
       </c>
       <c r="N3" t="n">
         <v>1610612748</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.5153</v>
+        <v>0.4935</v>
       </c>
       <c r="N4" t="n">
         <v>1610612753</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7155</v>
+        <v>0.7166</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7155</v>
+        <v>0.7166</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.4253</v>
+        <v>0.393</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.4253</v>
+        <v>0.393</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.7155</v>
+        <v>0.7166</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.4253</v>
+        <v>0.393</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7155</v>
+        <v>0.7166</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7544</v>
+        <v>0.7488</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7544</v>
+        <v>0.7488</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3548</v>
+        <v>0.354</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3548</v>
+        <v>0.354</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7544</v>
+        <v>0.7488</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3548</v>
+        <v>0.354</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7544</v>
+        <v>0.7488</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.725</v>
+        <v>0.7153</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.725</v>
+        <v>0.7153</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4</v>
+        <v>0.4212</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4</v>
+        <v>0.4212</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.725</v>
+        <v>0.7153</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4</v>
+        <v>0.4212</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.725</v>
+        <v>0.7153</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.6866</v>
+        <v>0.6904</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.6866</v>
+        <v>0.6904</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4476</v>
+        <v>0.4716</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4476</v>
+        <v>0.4716</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.6866</v>
+        <v>0.6904</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4476</v>
+        <v>0.4716</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.6866</v>
+        <v>0.6904</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4879</v>
+        <v>0.5078</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5969</v>
+        <v>0.5752</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.7009</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7319</v>
+        <v>0.7226</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7319</v>
+        <v>0.7226</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.3788</v>
+        <v>0.3647</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.3788</v>
+        <v>0.3647</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7319</v>
+        <v>0.7226</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.3788</v>
+        <v>0.3647</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7319</v>
+        <v>0.7226</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7869</v>
+        <v>0.7671</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7869</v>
+        <v>0.7671</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3246</v>
+        <v>0.3481</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3246</v>
+        <v>0.3481</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7869</v>
+        <v>0.7671</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3246</v>
+        <v>0.3481</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7869</v>
+        <v>0.7671</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6407</v>
+        <v>0.6633</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6407</v>
+        <v>0.6633</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.5299</v>
+        <v>0.5182</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.5299</v>
+        <v>0.5182</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6407</v>
+        <v>0.6633</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.5299</v>
+        <v>0.5182</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6407</v>
+        <v>0.6633</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6617</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6617</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4843</v>
+        <v>0.514</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4843</v>
+        <v>0.514</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6617</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4843</v>
+        <v>0.514</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6617</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.6029</v>
+        <v>0.6408</v>
       </c>
       <c r="N2" t="n">
         <v>1610612755</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.4934</v>
+        <v>0.4657</v>
       </c>
       <c r="N3" t="n">
         <v>1610612748</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4935</v>
+        <v>0.4956</v>
       </c>
       <c r="N4" t="n">
         <v>1610612753</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7166</v>
+        <v>0.7476</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7166</v>
+        <v>0.7476</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.393</v>
+        <v>0.3939</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.393</v>
+        <v>0.3939</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.7166</v>
+        <v>0.7476</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.393</v>
+        <v>0.3939</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7166</v>
+        <v>0.7476</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7488</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7488</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.354</v>
+        <v>0.3589</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.354</v>
+        <v>0.3589</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7488</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.354</v>
+        <v>0.3589</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7488</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7153</v>
+        <v>0.736</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7153</v>
+        <v>0.736</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4212</v>
+        <v>0.4191</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4212</v>
+        <v>0.4191</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.7153</v>
+        <v>0.736</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4212</v>
+        <v>0.4191</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.7153</v>
+        <v>0.736</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.6904</v>
+        <v>0.7427</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.6904</v>
+        <v>0.7427</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4716</v>
+        <v>0.4709</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4716</v>
+        <v>0.4709</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.6904</v>
+        <v>0.7427</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4716</v>
+        <v>0.4709</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.6904</v>
+        <v>0.7427</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.5078</v>
+        <v>0.4955</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5752</v>
+        <v>0.5712</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.7009</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>1610612746</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7226</v>
+        <v>0.7516</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7226</v>
+        <v>0.7516</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.3647</v>
+        <v>0.375</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.3647</v>
+        <v>0.375</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7226</v>
+        <v>0.7516</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.3647</v>
+        <v>0.375</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7226</v>
+        <v>0.7516</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7671</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7671</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3481</v>
+        <v>0.3503</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3481</v>
+        <v>0.3503</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7671</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3481</v>
+        <v>0.3503</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7671</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6633</v>
+        <v>0.6727</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6633</v>
+        <v>0.6727</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.5182</v>
+        <v>0.4991</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.5182</v>
+        <v>0.4991</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6633</v>
+        <v>0.6727</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.5182</v>
+        <v>0.4991</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6633</v>
+        <v>0.6727</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6617</v>
+        <v>0.6554</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6617</v>
+        <v>0.6554</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.514</v>
+        <v>0.4618</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.514</v>
+        <v>0.4618</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6617</v>
+        <v>0.6554</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.514</v>
+        <v>0.4618</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6617</v>
+        <v>0.6554</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -531,39 +531,39 @@
         <v>175</v>
       </c>
       <c r="G2" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.6408</v>
+        <v>0.4786</v>
       </c>
       <c r="N2" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="O2" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -600,39 +600,39 @@
         <v>176</v>
       </c>
       <c r="G3" t="n">
+        <v>1610612753</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>1610612748</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>MIA</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Miami Heat</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>1610612766</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>CHA</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Charlotte Hornets</t>
-        </is>
-      </c>
       <c r="M3" t="n">
-        <v>0.4657</v>
+        <v>0.5122</v>
       </c>
       <c r="N3" t="n">
+        <v>1610612753</v>
+      </c>
+      <c r="O3" t="n">
         <v>1610612748</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1610612766</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -669,39 +669,39 @@
         <v>178</v>
       </c>
       <c r="G4" t="n">
+        <v>1610612766</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>1610612753</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>ORL</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Orlando Magic</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>1610612748</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Miami Heat</t>
-        </is>
-      </c>
       <c r="M4" t="n">
-        <v>0.4956</v>
+        <v>0.7381</v>
       </c>
       <c r="N4" t="n">
+        <v>1610612766</v>
+      </c>
+      <c r="O4" t="n">
         <v>1610612753</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1610612748</v>
       </c>
       <c r="P4" t="n">
         <v>8</v>
@@ -751,26 +751,26 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7476</v>
+        <v>0.5837</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
       </c>
       <c r="O5" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -820,26 +820,26 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7476</v>
+        <v>0.5837</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
       </c>
       <c r="O6" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -876,16 +876,16 @@
         <v>184</v>
       </c>
       <c r="G7" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.3939</v>
+        <v>0.5637</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
       </c>
       <c r="O7" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -945,16 +945,16 @@
         <v>186</v>
       </c>
       <c r="G8" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -971,13 +971,13 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.3939</v>
+        <v>0.5637</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
       </c>
       <c r="O8" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1027,26 +1027,26 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.7476</v>
+        <v>0.5837</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
       </c>
       <c r="O9" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1083,16 +1083,16 @@
         <v>190</v>
       </c>
       <c r="G10" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.3939</v>
+        <v>0.5637</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
       </c>
       <c r="O10" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1165,26 +1165,26 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Orlando Magic</t>
+          <t>Charlotte Hornets</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7476</v>
+        <v>0.5837</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
       </c>
       <c r="O11" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1234,26 +1234,26 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7661</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
       </c>
       <c r="O12" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
@@ -1303,26 +1303,26 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7661</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
       </c>
       <c r="O13" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1359,16 +1359,16 @@
         <v>184</v>
       </c>
       <c r="G14" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.3589</v>
+        <v>0.4044</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
       </c>
       <c r="O14" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -1428,16 +1428,16 @@
         <v>186</v>
       </c>
       <c r="G15" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1454,13 +1454,13 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.3589</v>
+        <v>0.4044</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
       </c>
       <c r="O15" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
@@ -1510,26 +1510,26 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7661</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
       </c>
       <c r="O16" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
@@ -1566,16 +1566,16 @@
         <v>190</v>
       </c>
       <c r="G17" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3589</v>
+        <v>0.4044</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
       </c>
       <c r="O17" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -1648,26 +1648,26 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7661</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
       </c>
       <c r="O18" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1717,26 +1717,26 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.736</v>
+        <v>0.7351</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
       </c>
       <c r="O19" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.736</v>
+        <v>0.7351</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
       </c>
       <c r="O20" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
@@ -1842,16 +1842,16 @@
         <v>184</v>
       </c>
       <c r="G21" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.4191</v>
+        <v>0.3777</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
       </c>
       <c r="O21" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P21" t="n">
         <v>3</v>
@@ -1911,16 +1911,16 @@
         <v>186</v>
       </c>
       <c r="G22" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.4191</v>
+        <v>0.3777</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
       </c>
       <c r="O22" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -1993,26 +1993,26 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.736</v>
+        <v>0.7351</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
       </c>
       <c r="O23" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -2049,16 +2049,16 @@
         <v>190</v>
       </c>
       <c r="G24" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.4191</v>
+        <v>0.3777</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
       </c>
       <c r="O24" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
@@ -2131,26 +2131,26 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.736</v>
+        <v>0.7351</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
       </c>
       <c r="O25" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7427</v>
+        <v>0.733</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7427</v>
+        <v>0.733</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4709</v>
+        <v>0.4804</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4709</v>
+        <v>0.4804</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7427</v>
+        <v>0.733</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4709</v>
+        <v>0.4804</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7427</v>
+        <v>0.733</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4955</v>
+        <v>0.4992</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5712</v>
+        <v>0.5723</v>
       </c>
       <c r="N34" t="n">
         <v>1610612757</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7516</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7516</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7516</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7516</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7843</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7843</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3503</v>
+        <v>0.3482</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3503</v>
+        <v>0.3482</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7843</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3503</v>
+        <v>0.3482</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7843</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3856,26 +3856,26 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6727</v>
+        <v>0.6279</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
       </c>
       <c r="O50" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="P50" t="n">
         <v>3</v>
@@ -3925,26 +3925,26 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6727</v>
+        <v>0.6279</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
       </c>
       <c r="O51" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="P51" t="n">
         <v>3</v>
@@ -3981,16 +3981,16 @@
         <v>185</v>
       </c>
       <c r="G52" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -4007,13 +4007,13 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4991</v>
+        <v>0.5304</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
       </c>
       <c r="O52" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
@@ -4050,16 +4050,16 @@
         <v>187</v>
       </c>
       <c r="G53" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -4076,13 +4076,13 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.4991</v>
+        <v>0.5304</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
       </c>
       <c r="O53" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="P53" t="n">
         <v>3</v>
@@ -4132,26 +4132,26 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6727</v>
+        <v>0.6279</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
       </c>
       <c r="O54" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="P54" t="n">
         <v>3</v>
@@ -4188,16 +4188,16 @@
         <v>191</v>
       </c>
       <c r="G55" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.4991</v>
+        <v>0.5304</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
       </c>
       <c r="O55" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="P55" t="n">
         <v>3</v>
@@ -4270,26 +4270,26 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Houston Rockets</t>
+          <t>Minnesota Timberwolves</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6727</v>
+        <v>0.6279</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
       </c>
       <c r="O56" t="n">
-        <v>1610612745</v>
+        <v>1610612750</v>
       </c>
       <c r="P56" t="n">
         <v>3</v>
@@ -4339,26 +4339,26 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6554</v>
+        <v>0.6659</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
       </c>
       <c r="O57" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="P57" t="n">
         <v>4</v>
@@ -4408,26 +4408,26 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6554</v>
+        <v>0.6659</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
       </c>
       <c r="O58" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="P58" t="n">
         <v>4</v>
@@ -4464,16 +4464,16 @@
         <v>185</v>
       </c>
       <c r="G59" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -4490,13 +4490,13 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4618</v>
+        <v>0.4912</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
       </c>
       <c r="O59" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="P59" t="n">
         <v>4</v>
@@ -4533,16 +4533,16 @@
         <v>187</v>
       </c>
       <c r="G60" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -4559,13 +4559,13 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4618</v>
+        <v>0.4912</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
       </c>
       <c r="O60" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="P60" t="n">
         <v>4</v>
@@ -4615,26 +4615,26 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6554</v>
+        <v>0.6659</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
       </c>
       <c r="O61" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="P61" t="n">
         <v>4</v>
@@ -4671,16 +4671,16 @@
         <v>191</v>
       </c>
       <c r="G62" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -4697,13 +4697,13 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4618</v>
+        <v>0.4912</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
       </c>
       <c r="O62" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="P62" t="n">
         <v>4</v>
@@ -4753,26 +4753,26 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Minnesota Timberwolves</t>
+          <t>Houston Rockets</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6554</v>
+        <v>0.6659</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>
       </c>
       <c r="O63" t="n">
-        <v>1610612750</v>
+        <v>1610612745</v>
       </c>
       <c r="P63" t="n">
         <v>4</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.4786</v>
+        <v>0.4991</v>
       </c>
       <c r="N2" t="n">
         <v>1610612761</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7381</v>
+        <v>0.7346</v>
       </c>
       <c r="N4" t="n">
         <v>1610612766</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.5837</v>
+        <v>0.5849</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.5837</v>
+        <v>0.5849</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.5637</v>
+        <v>0.5447</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.5637</v>
+        <v>0.5447</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.5837</v>
+        <v>0.5849</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.5637</v>
+        <v>0.5447</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.5837</v>
+        <v>0.5849</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7661</v>
+        <v>0.7642</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7661</v>
+        <v>0.7642</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7661</v>
+        <v>0.7642</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7661</v>
+        <v>0.7642</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.733</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.733</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4804</v>
+        <v>0.4781</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4804</v>
+        <v>0.4781</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.733</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4804</v>
+        <v>0.4781</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.733</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2683,26 +2683,26 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.4992</v>
+        <v>0.6277</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
       </c>
       <c r="O33" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P33" t="n">
         <v>7</v>
@@ -2739,16 +2739,16 @@
         <v>176</v>
       </c>
       <c r="G34" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Portland Trail Blazers</t>
+          <t>LA Clippers</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.5723</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="O34" t="n">
         <v>1610612744</v>
@@ -2808,39 +2808,39 @@
         <v>178</v>
       </c>
       <c r="G35" t="n">
+        <v>1610612757</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
         <v>1610612746</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>LA Clippers</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="M35" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N35" t="n">
         <v>1610612757</v>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Portland Trail Blazers</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>0.7364000000000001</v>
-      </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>1610612746</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1610612757</v>
       </c>
       <c r="P35" t="n">
         <v>8</v>
@@ -2890,26 +2890,26 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.8136</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
       </c>
       <c r="O36" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -2959,26 +2959,26 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.8136</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
       </c>
       <c r="O37" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -3015,16 +3015,16 @@
         <v>185</v>
       </c>
       <c r="G38" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -3041,13 +3041,13 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.375</v>
+        <v>0.2432</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
       </c>
       <c r="O38" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3084,16 +3084,16 @@
         <v>187</v>
       </c>
       <c r="G39" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.375</v>
+        <v>0.2432</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
       </c>
       <c r="O39" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -3166,26 +3166,26 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.8136</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
       </c>
       <c r="O40" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3222,16 +3222,16 @@
         <v>191</v>
       </c>
       <c r="G41" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -3248,13 +3248,13 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.375</v>
+        <v>0.2432</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
       </c>
       <c r="O41" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3304,26 +3304,26 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>LA Clippers</t>
+          <t>Portland Trail Blazers</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.8136</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
       </c>
       <c r="O42" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.7843</v>
+        <v>0.8147</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.7843</v>
+        <v>0.8147</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3482</v>
+        <v>0.3459</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3482</v>
+        <v>0.3459</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.7843</v>
+        <v>0.8147</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3482</v>
+        <v>0.3459</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.7843</v>
+        <v>0.8147</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6279</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6279</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.5304</v>
+        <v>0.5244</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.5304</v>
+        <v>0.5244</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6279</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.5304</v>
+        <v>0.5244</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6279</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6659</v>
+        <v>0.6609</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6659</v>
+        <v>0.6609</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.4912</v>
+        <v>0.5029</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.4912</v>
+        <v>0.5029</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6659</v>
+        <v>0.6609</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.4912</v>
+        <v>0.5029</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6659</v>
+        <v>0.6609</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7642</v>
+        <v>0.7661</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7642</v>
+        <v>0.7661</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7642</v>
+        <v>0.7661</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642</v>
+        <v>0.7661</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7351</v>
+        <v>0.6846</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7351</v>
+        <v>0.6846</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.3777</v>
+        <v>0.3934</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.3777</v>
+        <v>0.3934</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.7351</v>
+        <v>0.6846</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.3777</v>
+        <v>0.3934</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.7351</v>
+        <v>0.6846</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.8136</v>
+        <v>0.8149</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.8136</v>
+        <v>0.8149</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.2432</v>
+        <v>0.2416</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.2432</v>
+        <v>0.2416</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.8136</v>
+        <v>0.8149</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.2432</v>
+        <v>0.2416</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.8136</v>
+        <v>0.8149</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6165</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6165</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6165</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6165</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.5447</v>
+        <v>0.5457</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.5447</v>
+        <v>0.5457</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.5447</v>
+        <v>0.5457</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7661</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7661</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7661</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7661</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7307</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7307</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4781</v>
+        <v>0.4733</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4781</v>
+        <v>0.4733</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7307</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4781</v>
+        <v>0.4733</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7307</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.6277</v>
+        <v>0.5866</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.49</v>
+        <v>0.514</v>
       </c>
       <c r="N35" t="n">
         <v>1610612757</v>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.8149</v>
+        <v>0.8061</v>
       </c>
       <c r="N36" t="n">
         <v>1610612760</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.8149</v>
+        <v>0.8061</v>
       </c>
       <c r="N37" t="n">
         <v>1610612760</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.2416</v>
+        <v>0.2472</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.2416</v>
+        <v>0.2472</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.8149</v>
+        <v>0.8061</v>
       </c>
       <c r="N40" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.2416</v>
+        <v>0.2472</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.8149</v>
+        <v>0.8061</v>
       </c>
       <c r="N42" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.8147</v>
+        <v>0.8166</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.8147</v>
+        <v>0.8166</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3459</v>
+        <v>0.3398</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3459</v>
+        <v>0.3398</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.8147</v>
+        <v>0.8166</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3459</v>
+        <v>0.3398</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.8147</v>
+        <v>0.8166</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.6165</v>
+        <v>0.4961</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.6165</v>
+        <v>0.4961</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.5244</v>
+        <v>0.6269</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.5244</v>
+        <v>0.6269</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.6165</v>
+        <v>0.4961</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.5244</v>
+        <v>0.6269</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.6165</v>
+        <v>0.4961</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6609</v>
+        <v>0.6634</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6609</v>
+        <v>0.6634</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.5029</v>
+        <v>0.498</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.5029</v>
+        <v>0.498</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6609</v>
+        <v>0.6634</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.5029</v>
+        <v>0.498</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6609</v>
+        <v>0.6634</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.4991</v>
+        <v>0.4814</v>
       </c>
       <c r="N2" t="n">
         <v>1610612761</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7346</v>
+        <v>0.7513</v>
       </c>
       <c r="N4" t="n">
         <v>1610612766</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.5849</v>
+        <v>0.5799</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.5849</v>
+        <v>0.5799</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.5457</v>
+        <v>0.5702</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.5457</v>
+        <v>0.5702</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.5849</v>
+        <v>0.5799</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.5457</v>
+        <v>0.5702</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.5849</v>
+        <v>0.5799</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.514</v>
+        <v>0.5073</v>
       </c>
       <c r="N35" t="n">
         <v>1610612757</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.498</v>
+        <v>0.496</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.498</v>
+        <v>0.496</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.498</v>
+        <v>0.496</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -531,16 +531,16 @@
         <v>175</v>
       </c>
       <c r="G2" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.4814</v>
+        <v>0.4837</v>
       </c>
       <c r="N2" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="O2" t="n">
         <v>1610612766</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.5122</v>
+        <v>0.4909</v>
       </c>
       <c r="N3" t="n">
         <v>1610612753</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7513</v>
+        <v>0.7582</v>
       </c>
       <c r="N4" t="n">
         <v>1610612766</v>
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.5799</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="N5" t="n">
         <v>1610612765</v>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.5799</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="N6" t="n">
         <v>1610612765</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.5702</v>
+        <v>0.5525</v>
       </c>
       <c r="N7" t="n">
         <v>1610612765</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.5702</v>
+        <v>0.5525</v>
       </c>
       <c r="N8" t="n">
         <v>1610612765</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.5799</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>1610612765</v>
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.5702</v>
+        <v>0.5525</v>
       </c>
       <c r="N10" t="n">
         <v>1610612765</v>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.5799</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>1610612765</v>
@@ -1234,26 +1234,26 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7778</v>
       </c>
       <c r="N12" t="n">
         <v>1610612738</v>
       </c>
       <c r="O12" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
@@ -1303,26 +1303,26 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7778</v>
       </c>
       <c r="N13" t="n">
         <v>1610612738</v>
       </c>
       <c r="O13" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -1359,16 +1359,16 @@
         <v>184</v>
       </c>
       <c r="G14" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.4044</v>
+        <v>0.3457</v>
       </c>
       <c r="N14" t="n">
         <v>1610612738</v>
       </c>
       <c r="O14" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -1428,16 +1428,16 @@
         <v>186</v>
       </c>
       <c r="G15" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1454,13 +1454,13 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.4044</v>
+        <v>0.3457</v>
       </c>
       <c r="N15" t="n">
         <v>1610612738</v>
       </c>
       <c r="O15" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
@@ -1510,26 +1510,26 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7778</v>
       </c>
       <c r="N16" t="n">
         <v>1610612738</v>
       </c>
       <c r="O16" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
@@ -1566,16 +1566,16 @@
         <v>190</v>
       </c>
       <c r="G17" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.4044</v>
+        <v>0.3457</v>
       </c>
       <c r="N17" t="n">
         <v>1610612738</v>
       </c>
       <c r="O17" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -1648,26 +1648,26 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Toronto Raptors</t>
+          <t>Philadelphia 76ers</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7778</v>
       </c>
       <c r="N18" t="n">
         <v>1610612738</v>
       </c>
       <c r="O18" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
@@ -1717,26 +1717,26 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.6846</v>
+        <v>0.7506</v>
       </c>
       <c r="N19" t="n">
         <v>1610612752</v>
       </c>
       <c r="O19" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -1786,26 +1786,26 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.6846</v>
+        <v>0.7506</v>
       </c>
       <c r="N20" t="n">
         <v>1610612752</v>
       </c>
       <c r="O20" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
@@ -1842,16 +1842,16 @@
         <v>184</v>
       </c>
       <c r="G21" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.3934</v>
+        <v>0.4181</v>
       </c>
       <c r="N21" t="n">
         <v>1610612752</v>
       </c>
       <c r="O21" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P21" t="n">
         <v>3</v>
@@ -1911,16 +1911,16 @@
         <v>186</v>
       </c>
       <c r="G22" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.3934</v>
+        <v>0.4181</v>
       </c>
       <c r="N22" t="n">
         <v>1610612752</v>
       </c>
       <c r="O22" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -1993,26 +1993,26 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.6846</v>
+        <v>0.7506</v>
       </c>
       <c r="N23" t="n">
         <v>1610612752</v>
       </c>
       <c r="O23" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -2049,16 +2049,16 @@
         <v>190</v>
       </c>
       <c r="G24" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.3934</v>
+        <v>0.4181</v>
       </c>
       <c r="N24" t="n">
         <v>1610612752</v>
       </c>
       <c r="O24" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P24" t="n">
         <v>3</v>
@@ -2131,26 +2131,26 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Philadelphia 76ers</t>
+          <t>Toronto Raptors</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.6846</v>
+        <v>0.7506</v>
       </c>
       <c r="N25" t="n">
         <v>1610612752</v>
       </c>
       <c r="O25" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.7307</v>
+        <v>0.6463</v>
       </c>
       <c r="N26" t="n">
         <v>1610612739</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.7307</v>
+        <v>0.6463</v>
       </c>
       <c r="N27" t="n">
         <v>1610612739</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.4733</v>
+        <v>0.5175</v>
       </c>
       <c r="N28" t="n">
         <v>1610612739</v>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.4733</v>
+        <v>0.5175</v>
       </c>
       <c r="N29" t="n">
         <v>1610612739</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.7307</v>
+        <v>0.6463</v>
       </c>
       <c r="N30" t="n">
         <v>1610612739</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.4733</v>
+        <v>0.5175</v>
       </c>
       <c r="N31" t="n">
         <v>1610612739</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.7307</v>
+        <v>0.6463</v>
       </c>
       <c r="N32" t="n">
         <v>1610612739</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.5866</v>
+        <v>0.5876</v>
       </c>
       <c r="N33" t="n">
         <v>1610612756</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="N34" t="n">
         <v>1610612746</v>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.5073</v>
+        <v>0.515</v>
       </c>
       <c r="N35" t="n">
         <v>1610612757</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.2472</v>
+        <v>0.2479</v>
       </c>
       <c r="N38" t="n">
         <v>1610612760</v>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.2472</v>
+        <v>0.2479</v>
       </c>
       <c r="N39" t="n">
         <v>1610612760</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.2472</v>
+        <v>0.2479</v>
       </c>
       <c r="N41" t="n">
         <v>1610612760</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>0.8166</v>
+        <v>0.8162</v>
       </c>
       <c r="N43" t="n">
         <v>1610612759</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0.8166</v>
+        <v>0.8162</v>
       </c>
       <c r="N44" t="n">
         <v>1610612759</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>0.3398</v>
+        <v>0.3358</v>
       </c>
       <c r="N45" t="n">
         <v>1610612759</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.3398</v>
+        <v>0.3358</v>
       </c>
       <c r="N46" t="n">
         <v>1610612759</v>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.8166</v>
+        <v>0.8162</v>
       </c>
       <c r="N47" t="n">
         <v>1610612759</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>0.3398</v>
+        <v>0.3358</v>
       </c>
       <c r="N48" t="n">
         <v>1610612759</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.8166</v>
+        <v>0.8162</v>
       </c>
       <c r="N49" t="n">
         <v>1610612759</v>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.4961</v>
+        <v>0.4659</v>
       </c>
       <c r="N50" t="n">
         <v>1610612747</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.4961</v>
+        <v>0.4659</v>
       </c>
       <c r="N51" t="n">
         <v>1610612747</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.6269</v>
+        <v>0.6691</v>
       </c>
       <c r="N52" t="n">
         <v>1610612747</v>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0.6269</v>
+        <v>0.6691</v>
       </c>
       <c r="N53" t="n">
         <v>1610612747</v>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.4961</v>
+        <v>0.4659</v>
       </c>
       <c r="N54" t="n">
         <v>1610612747</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.6269</v>
+        <v>0.6691</v>
       </c>
       <c r="N55" t="n">
         <v>1610612747</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.4961</v>
+        <v>0.4659</v>
       </c>
       <c r="N56" t="n">
         <v>1610612747</v>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.6634</v>
+        <v>0.6548</v>
       </c>
       <c r="N57" t="n">
         <v>1610612743</v>
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.6634</v>
+        <v>0.6548</v>
       </c>
       <c r="N58" t="n">
         <v>1610612743</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.496</v>
+        <v>0.5213</v>
       </c>
       <c r="N59" t="n">
         <v>1610612743</v>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.496</v>
+        <v>0.5213</v>
       </c>
       <c r="N60" t="n">
         <v>1610612743</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.6634</v>
+        <v>0.6548</v>
       </c>
       <c r="N61" t="n">
         <v>1610612743</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.496</v>
+        <v>0.5213</v>
       </c>
       <c r="N62" t="n">
         <v>1610612743</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.6634</v>
+        <v>0.6548</v>
       </c>
       <c r="N63" t="n">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -794,7 +794,7 @@
         <v>90</v>
       </c>
       <c r="M3">
-        <v>0.5002</v>
+        <v>0.502</v>
       </c>
       <c r="N3">
         <v>1610612753</v>
@@ -1271,7 +1271,7 @@
         <v>70</v>
       </c>
       <c r="M12">
-        <v>0.8053</v>
+        <v>0.8026</v>
       </c>
       <c r="N12">
         <v>1610612738</v>
@@ -1324,7 +1324,7 @@
         <v>70</v>
       </c>
       <c r="M13">
-        <v>0.8053</v>
+        <v>0.8026</v>
       </c>
       <c r="N13">
         <v>1610612738</v>
@@ -1483,7 +1483,7 @@
         <v>70</v>
       </c>
       <c r="M16">
-        <v>0.8053</v>
+        <v>0.8026</v>
       </c>
       <c r="N16">
         <v>1610612738</v>
@@ -1589,7 +1589,7 @@
         <v>70</v>
       </c>
       <c r="M18">
-        <v>0.8053</v>
+        <v>0.8026</v>
       </c>
       <c r="N18">
         <v>1610612738</v>
@@ -1642,7 +1642,7 @@
         <v>76</v>
       </c>
       <c r="M19">
-        <v>0.7425</v>
+        <v>0.7239</v>
       </c>
       <c r="N19">
         <v>1610612752</v>
@@ -1695,7 +1695,7 @@
         <v>76</v>
       </c>
       <c r="M20">
-        <v>0.7425</v>
+        <v>0.7239</v>
       </c>
       <c r="N20">
         <v>1610612752</v>
@@ -1748,7 +1748,7 @@
         <v>75</v>
       </c>
       <c r="M21">
-        <v>0.4297</v>
+        <v>0.438</v>
       </c>
       <c r="N21">
         <v>1610612752</v>
@@ -1801,7 +1801,7 @@
         <v>75</v>
       </c>
       <c r="M22">
-        <v>0.4297</v>
+        <v>0.438</v>
       </c>
       <c r="N22">
         <v>1610612752</v>
@@ -1854,7 +1854,7 @@
         <v>76</v>
       </c>
       <c r="M23">
-        <v>0.7425</v>
+        <v>0.7239</v>
       </c>
       <c r="N23">
         <v>1610612752</v>
@@ -1907,7 +1907,7 @@
         <v>75</v>
       </c>
       <c r="M24">
-        <v>0.4297</v>
+        <v>0.438</v>
       </c>
       <c r="N24">
         <v>1610612752</v>
@@ -1960,7 +1960,7 @@
         <v>76</v>
       </c>
       <c r="M25">
-        <v>0.7425</v>
+        <v>0.7239</v>
       </c>
       <c r="N25">
         <v>1610612752</v>
@@ -2013,7 +2013,7 @@
         <v>78</v>
       </c>
       <c r="M26">
-        <v>0.7013</v>
+        <v>0.6975</v>
       </c>
       <c r="N26">
         <v>1610612739</v>
@@ -2066,7 +2066,7 @@
         <v>78</v>
       </c>
       <c r="M27">
-        <v>0.7013</v>
+        <v>0.6975</v>
       </c>
       <c r="N27">
         <v>1610612739</v>
@@ -2225,7 +2225,7 @@
         <v>78</v>
       </c>
       <c r="M30">
-        <v>0.7013</v>
+        <v>0.6975</v>
       </c>
       <c r="N30">
         <v>1610612739</v>
@@ -2331,7 +2331,7 @@
         <v>78</v>
       </c>
       <c r="M32">
-        <v>0.7013</v>
+        <v>0.6975</v>
       </c>
       <c r="N32">
         <v>1610612739</v>
@@ -2384,7 +2384,7 @@
         <v>81</v>
       </c>
       <c r="M33">
-        <v>0.4917</v>
+        <v>0.4934</v>
       </c>
       <c r="N33">
         <v>1610612756</v>
@@ -2437,7 +2437,7 @@
         <v>91</v>
       </c>
       <c r="M34">
-        <v>0.5793</v>
+        <v>0.581</v>
       </c>
       <c r="N34">
         <v>1610612757</v>
@@ -2543,7 +2543,7 @@
         <v>81</v>
       </c>
       <c r="M36">
-        <v>0.77</v>
+        <v>0.7739</v>
       </c>
       <c r="N36">
         <v>1610612760</v>
@@ -2596,7 +2596,7 @@
         <v>81</v>
       </c>
       <c r="M37">
-        <v>0.77</v>
+        <v>0.7739</v>
       </c>
       <c r="N37">
         <v>1610612760</v>
@@ -2755,7 +2755,7 @@
         <v>81</v>
       </c>
       <c r="M40">
-        <v>0.77</v>
+        <v>0.7739</v>
       </c>
       <c r="N40">
         <v>1610612760</v>
@@ -2861,7 +2861,7 @@
         <v>81</v>
       </c>
       <c r="M42">
-        <v>0.77</v>
+        <v>0.7739</v>
       </c>
       <c r="N42">
         <v>1610612760</v>
@@ -2914,7 +2914,7 @@
         <v>79</v>
       </c>
       <c r="M43">
-        <v>0.7989000000000001</v>
+        <v>0.7975</v>
       </c>
       <c r="N43">
         <v>1610612759</v>
@@ -2967,7 +2967,7 @@
         <v>79</v>
       </c>
       <c r="M44">
-        <v>0.7989000000000001</v>
+        <v>0.7975</v>
       </c>
       <c r="N44">
         <v>1610612759</v>
@@ -3020,7 +3020,7 @@
         <v>83</v>
       </c>
       <c r="M45">
-        <v>0.3376</v>
+        <v>0.3402</v>
       </c>
       <c r="N45">
         <v>1610612759</v>
@@ -3073,7 +3073,7 @@
         <v>83</v>
       </c>
       <c r="M46">
-        <v>0.3376</v>
+        <v>0.3402</v>
       </c>
       <c r="N46">
         <v>1610612759</v>
@@ -3126,7 +3126,7 @@
         <v>79</v>
       </c>
       <c r="M47">
-        <v>0.7989000000000001</v>
+        <v>0.7975</v>
       </c>
       <c r="N47">
         <v>1610612759</v>
@@ -3179,7 +3179,7 @@
         <v>83</v>
       </c>
       <c r="M48">
-        <v>0.3376</v>
+        <v>0.3402</v>
       </c>
       <c r="N48">
         <v>1610612759</v>
@@ -3232,7 +3232,7 @@
         <v>79</v>
       </c>
       <c r="M49">
-        <v>0.7989000000000001</v>
+        <v>0.7975</v>
       </c>
       <c r="N49">
         <v>1610612759</v>
@@ -3285,7 +3285,7 @@
         <v>85</v>
       </c>
       <c r="M50">
-        <v>0.5869</v>
+        <v>0.7121</v>
       </c>
       <c r="N50">
         <v>1610612743</v>
@@ -3338,7 +3338,7 @@
         <v>85</v>
       </c>
       <c r="M51">
-        <v>0.5869</v>
+        <v>0.7121</v>
       </c>
       <c r="N51">
         <v>1610612743</v>
@@ -3391,7 +3391,7 @@
         <v>84</v>
       </c>
       <c r="M52">
-        <v>0.5345</v>
+        <v>0.4264</v>
       </c>
       <c r="N52">
         <v>1610612743</v>
@@ -3444,7 +3444,7 @@
         <v>84</v>
       </c>
       <c r="M53">
-        <v>0.5345</v>
+        <v>0.4264</v>
       </c>
       <c r="N53">
         <v>1610612743</v>
@@ -3497,7 +3497,7 @@
         <v>85</v>
       </c>
       <c r="M54">
-        <v>0.5869</v>
+        <v>0.7121</v>
       </c>
       <c r="N54">
         <v>1610612743</v>
@@ -3550,7 +3550,7 @@
         <v>84</v>
       </c>
       <c r="M55">
-        <v>0.5345</v>
+        <v>0.4264</v>
       </c>
       <c r="N55">
         <v>1610612743</v>
@@ -3603,7 +3603,7 @@
         <v>85</v>
       </c>
       <c r="M56">
-        <v>0.5869</v>
+        <v>0.7121</v>
       </c>
       <c r="N56">
         <v>1610612743</v>
@@ -3762,7 +3762,7 @@
         <v>86</v>
       </c>
       <c r="M59">
-        <v>0.7115</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="N59">
         <v>1610612747</v>
@@ -3815,7 +3815,7 @@
         <v>86</v>
       </c>
       <c r="M60">
-        <v>0.7115</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="N60">
         <v>1610612747</v>
@@ -3921,7 +3921,7 @@
         <v>86</v>
       </c>
       <c r="M62">
-        <v>0.7115</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="N62">
         <v>1610612747</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -172,15 +172,15 @@
     <t>2026-05-02</t>
   </si>
   <si>
+    <t>ORL</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
     <t>PHI</t>
   </si>
   <si>
-    <t>ORL</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
     <t>DET</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>NYK</t>
   </si>
   <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
     <t>TOR</t>
   </si>
   <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
     <t>PHX</t>
   </si>
   <si>
@@ -226,15 +226,15 @@
     <t>HOU</t>
   </si>
   <si>
+    <t>Orlando Magic</t>
+  </si>
+  <si>
+    <t>Charlotte Hornets</t>
+  </si>
+  <si>
     <t>Philadelphia 76ers</t>
   </si>
   <si>
-    <t>Orlando Magic</t>
-  </si>
-  <si>
-    <t>Charlotte Hornets</t>
-  </si>
-  <si>
     <t>Detroit Pistons</t>
   </si>
   <si>
@@ -244,13 +244,13 @@
     <t>New York Knicks</t>
   </si>
   <si>
+    <t>Atlanta Hawks</t>
+  </si>
+  <si>
+    <t>Cleveland Cavaliers</t>
+  </si>
+  <si>
     <t>Toronto Raptors</t>
-  </si>
-  <si>
-    <t>Cleveland Cavaliers</t>
-  </si>
-  <si>
-    <t>Atlanta Hawks</t>
   </si>
   <si>
     <t>Phoenix Suns</t>
@@ -723,7 +723,7 @@
         <v>175</v>
       </c>
       <c r="G2">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="H2" t="s">
         <v>52</v>
@@ -732,7 +732,7 @@
         <v>70</v>
       </c>
       <c r="J2">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="K2" t="s">
         <v>54</v>
@@ -741,13 +741,13 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>0.4798</v>
+        <v>0.5609</v>
       </c>
       <c r="N2">
+        <v>1610612753</v>
+      </c>
+      <c r="O2">
         <v>1610612755</v>
-      </c>
-      <c r="O2">
-        <v>1610612766</v>
       </c>
       <c r="P2">
         <v>7</v>
@@ -776,7 +776,7 @@
         <v>176</v>
       </c>
       <c r="G3">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="H3" t="s">
         <v>53</v>
@@ -794,10 +794,10 @@
         <v>90</v>
       </c>
       <c r="M3">
-        <v>0.502</v>
+        <v>0.7012</v>
       </c>
       <c r="N3">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="O3">
         <v>1610612748</v>
@@ -829,7 +829,7 @@
         <v>178</v>
       </c>
       <c r="G4">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="H4" t="s">
         <v>54</v>
@@ -838,7 +838,7 @@
         <v>72</v>
       </c>
       <c r="J4">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="K4" t="s">
         <v>53</v>
@@ -847,13 +847,13 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>0.7508</v>
+        <v>0.4403</v>
       </c>
       <c r="N4">
+        <v>1610612755</v>
+      </c>
+      <c r="O4">
         <v>1610612766</v>
-      </c>
-      <c r="O4">
-        <v>1610612753</v>
       </c>
       <c r="P4">
         <v>8</v>
@@ -891,7 +891,7 @@
         <v>73</v>
       </c>
       <c r="J5">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="K5" t="s">
         <v>54</v>
@@ -900,13 +900,13 @@
         <v>72</v>
       </c>
       <c r="M5">
-        <v>0.5835</v>
+        <v>0.7683</v>
       </c>
       <c r="N5">
         <v>1610612765</v>
       </c>
       <c r="O5">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -944,7 +944,7 @@
         <v>73</v>
       </c>
       <c r="J6">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="K6" t="s">
         <v>54</v>
@@ -953,13 +953,13 @@
         <v>72</v>
       </c>
       <c r="M6">
-        <v>0.5835</v>
+        <v>0.7683</v>
       </c>
       <c r="N6">
         <v>1610612765</v>
       </c>
       <c r="O6">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -988,7 +988,7 @@
         <v>184</v>
       </c>
       <c r="G7">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="H7" t="s">
         <v>54</v>
@@ -1006,13 +1006,13 @@
         <v>73</v>
       </c>
       <c r="M7">
-        <v>0.5642</v>
+        <v>0.3751</v>
       </c>
       <c r="N7">
         <v>1610612765</v>
       </c>
       <c r="O7">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -1041,7 +1041,7 @@
         <v>186</v>
       </c>
       <c r="G8">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="H8" t="s">
         <v>54</v>
@@ -1059,13 +1059,13 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>0.5642</v>
+        <v>0.3751</v>
       </c>
       <c r="N8">
         <v>1610612765</v>
       </c>
       <c r="O8">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>73</v>
       </c>
       <c r="J9">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="K9" t="s">
         <v>54</v>
@@ -1112,13 +1112,13 @@
         <v>72</v>
       </c>
       <c r="M9">
-        <v>0.5835</v>
+        <v>0.7683</v>
       </c>
       <c r="N9">
         <v>1610612765</v>
       </c>
       <c r="O9">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -1147,7 +1147,7 @@
         <v>190</v>
       </c>
       <c r="G10">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="H10" t="s">
         <v>54</v>
@@ -1165,13 +1165,13 @@
         <v>73</v>
       </c>
       <c r="M10">
-        <v>0.5642</v>
+        <v>0.3751</v>
       </c>
       <c r="N10">
         <v>1610612765</v>
       </c>
       <c r="O10">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1209,7 +1209,7 @@
         <v>73</v>
       </c>
       <c r="J11">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="K11" t="s">
         <v>54</v>
@@ -1218,13 +1218,13 @@
         <v>72</v>
       </c>
       <c r="M11">
-        <v>0.5835</v>
+        <v>0.7683</v>
       </c>
       <c r="N11">
         <v>1610612765</v>
       </c>
       <c r="O11">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -1262,7 +1262,7 @@
         <v>74</v>
       </c>
       <c r="J12">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="K12" t="s">
         <v>52</v>
@@ -1271,13 +1271,13 @@
         <v>70</v>
       </c>
       <c r="M12">
-        <v>0.8026</v>
+        <v>0.8181</v>
       </c>
       <c r="N12">
         <v>1610612738</v>
       </c>
       <c r="O12">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P12">
         <v>2</v>
@@ -1315,7 +1315,7 @@
         <v>74</v>
       </c>
       <c r="J13">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="K13" t="s">
         <v>52</v>
@@ -1324,13 +1324,13 @@
         <v>70</v>
       </c>
       <c r="M13">
-        <v>0.8026</v>
+        <v>0.8181</v>
       </c>
       <c r="N13">
         <v>1610612738</v>
       </c>
       <c r="O13">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P13">
         <v>2</v>
@@ -1359,7 +1359,7 @@
         <v>184</v>
       </c>
       <c r="G14">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="H14" t="s">
         <v>52</v>
@@ -1377,13 +1377,13 @@
         <v>74</v>
       </c>
       <c r="M14">
-        <v>0.3339</v>
+        <v>0.3204</v>
       </c>
       <c r="N14">
         <v>1610612738</v>
       </c>
       <c r="O14">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P14">
         <v>2</v>
@@ -1412,7 +1412,7 @@
         <v>186</v>
       </c>
       <c r="G15">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="H15" t="s">
         <v>52</v>
@@ -1430,13 +1430,13 @@
         <v>74</v>
       </c>
       <c r="M15">
-        <v>0.3339</v>
+        <v>0.3204</v>
       </c>
       <c r="N15">
         <v>1610612738</v>
       </c>
       <c r="O15">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P15">
         <v>2</v>
@@ -1474,7 +1474,7 @@
         <v>74</v>
       </c>
       <c r="J16">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="K16" t="s">
         <v>52</v>
@@ -1483,13 +1483,13 @@
         <v>70</v>
       </c>
       <c r="M16">
-        <v>0.8026</v>
+        <v>0.8181</v>
       </c>
       <c r="N16">
         <v>1610612738</v>
       </c>
       <c r="O16">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P16">
         <v>2</v>
@@ -1518,7 +1518,7 @@
         <v>190</v>
       </c>
       <c r="G17">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="H17" t="s">
         <v>52</v>
@@ -1536,13 +1536,13 @@
         <v>74</v>
       </c>
       <c r="M17">
-        <v>0.3339</v>
+        <v>0.3204</v>
       </c>
       <c r="N17">
         <v>1610612738</v>
       </c>
       <c r="O17">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P17">
         <v>2</v>
@@ -1580,7 +1580,7 @@
         <v>74</v>
       </c>
       <c r="J18">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="K18" t="s">
         <v>52</v>
@@ -1589,13 +1589,13 @@
         <v>70</v>
       </c>
       <c r="M18">
-        <v>0.8026</v>
+        <v>0.8181</v>
       </c>
       <c r="N18">
         <v>1610612738</v>
       </c>
       <c r="O18">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P18">
         <v>2</v>
@@ -1633,7 +1633,7 @@
         <v>75</v>
       </c>
       <c r="J19">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K19" t="s">
         <v>58</v>
@@ -1642,13 +1642,13 @@
         <v>76</v>
       </c>
       <c r="M19">
-        <v>0.7239</v>
+        <v>0.7002</v>
       </c>
       <c r="N19">
         <v>1610612752</v>
       </c>
       <c r="O19">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P19">
         <v>3</v>
@@ -1686,7 +1686,7 @@
         <v>75</v>
       </c>
       <c r="J20">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K20" t="s">
         <v>58</v>
@@ -1695,13 +1695,13 @@
         <v>76</v>
       </c>
       <c r="M20">
-        <v>0.7239</v>
+        <v>0.7002</v>
       </c>
       <c r="N20">
         <v>1610612752</v>
       </c>
       <c r="O20">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P20">
         <v>3</v>
@@ -1730,7 +1730,7 @@
         <v>184</v>
       </c>
       <c r="G21">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H21" t="s">
         <v>58</v>
@@ -1748,13 +1748,13 @@
         <v>75</v>
       </c>
       <c r="M21">
-        <v>0.438</v>
+        <v>0.4653</v>
       </c>
       <c r="N21">
         <v>1610612752</v>
       </c>
       <c r="O21">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P21">
         <v>3</v>
@@ -1783,7 +1783,7 @@
         <v>186</v>
       </c>
       <c r="G22">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H22" t="s">
         <v>58</v>
@@ -1801,13 +1801,13 @@
         <v>75</v>
       </c>
       <c r="M22">
-        <v>0.438</v>
+        <v>0.4653</v>
       </c>
       <c r="N22">
         <v>1610612752</v>
       </c>
       <c r="O22">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P22">
         <v>3</v>
@@ -1845,7 +1845,7 @@
         <v>75</v>
       </c>
       <c r="J23">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K23" t="s">
         <v>58</v>
@@ -1854,13 +1854,13 @@
         <v>76</v>
       </c>
       <c r="M23">
-        <v>0.7239</v>
+        <v>0.7002</v>
       </c>
       <c r="N23">
         <v>1610612752</v>
       </c>
       <c r="O23">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P23">
         <v>3</v>
@@ -1889,7 +1889,7 @@
         <v>190</v>
       </c>
       <c r="G24">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="H24" t="s">
         <v>58</v>
@@ -1907,13 +1907,13 @@
         <v>75</v>
       </c>
       <c r="M24">
-        <v>0.438</v>
+        <v>0.4653</v>
       </c>
       <c r="N24">
         <v>1610612752</v>
       </c>
       <c r="O24">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P24">
         <v>3</v>
@@ -1951,7 +1951,7 @@
         <v>75</v>
       </c>
       <c r="J25">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="K25" t="s">
         <v>58</v>
@@ -1960,13 +1960,13 @@
         <v>76</v>
       </c>
       <c r="M25">
-        <v>0.7239</v>
+        <v>0.7002</v>
       </c>
       <c r="N25">
         <v>1610612752</v>
       </c>
       <c r="O25">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="P25">
         <v>3</v>
@@ -2004,7 +2004,7 @@
         <v>77</v>
       </c>
       <c r="J26">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K26" t="s">
         <v>60</v>
@@ -2013,13 +2013,13 @@
         <v>78</v>
       </c>
       <c r="M26">
-        <v>0.6975</v>
+        <v>0.5843</v>
       </c>
       <c r="N26">
         <v>1610612739</v>
       </c>
       <c r="O26">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P26">
         <v>4</v>
@@ -2057,7 +2057,7 @@
         <v>77</v>
       </c>
       <c r="J27">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K27" t="s">
         <v>60</v>
@@ -2066,13 +2066,13 @@
         <v>78</v>
       </c>
       <c r="M27">
-        <v>0.6975</v>
+        <v>0.5843</v>
       </c>
       <c r="N27">
         <v>1610612739</v>
       </c>
       <c r="O27">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P27">
         <v>4</v>
@@ -2101,7 +2101,7 @@
         <v>184</v>
       </c>
       <c r="G28">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H28" t="s">
         <v>60</v>
@@ -2119,13 +2119,13 @@
         <v>77</v>
       </c>
       <c r="M28">
-        <v>0.4679</v>
+        <v>0.5152</v>
       </c>
       <c r="N28">
         <v>1610612739</v>
       </c>
       <c r="O28">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P28">
         <v>4</v>
@@ -2154,7 +2154,7 @@
         <v>186</v>
       </c>
       <c r="G29">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H29" t="s">
         <v>60</v>
@@ -2172,13 +2172,13 @@
         <v>77</v>
       </c>
       <c r="M29">
-        <v>0.4679</v>
+        <v>0.5152</v>
       </c>
       <c r="N29">
         <v>1610612739</v>
       </c>
       <c r="O29">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P29">
         <v>4</v>
@@ -2216,7 +2216,7 @@
         <v>77</v>
       </c>
       <c r="J30">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K30" t="s">
         <v>60</v>
@@ -2225,13 +2225,13 @@
         <v>78</v>
       </c>
       <c r="M30">
-        <v>0.6975</v>
+        <v>0.5843</v>
       </c>
       <c r="N30">
         <v>1610612739</v>
       </c>
       <c r="O30">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P30">
         <v>4</v>
@@ -2260,7 +2260,7 @@
         <v>190</v>
       </c>
       <c r="G31">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="H31" t="s">
         <v>60</v>
@@ -2278,13 +2278,13 @@
         <v>77</v>
       </c>
       <c r="M31">
-        <v>0.4679</v>
+        <v>0.5152</v>
       </c>
       <c r="N31">
         <v>1610612739</v>
       </c>
       <c r="O31">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P31">
         <v>4</v>
@@ -2322,7 +2322,7 @@
         <v>77</v>
       </c>
       <c r="J32">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="K32" t="s">
         <v>60</v>
@@ -2331,13 +2331,13 @@
         <v>78</v>
       </c>
       <c r="M32">
-        <v>0.6975</v>
+        <v>0.5843</v>
       </c>
       <c r="N32">
         <v>1610612739</v>
       </c>
       <c r="O32">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="P32">
         <v>4</v>
@@ -2384,7 +2384,7 @@
         <v>81</v>
       </c>
       <c r="M33">
-        <v>0.4934</v>
+        <v>0.4634</v>
       </c>
       <c r="N33">
         <v>1610612756</v>
@@ -2437,7 +2437,7 @@
         <v>91</v>
       </c>
       <c r="M34">
-        <v>0.581</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="N34">
         <v>1610612757</v>
@@ -2490,7 +2490,7 @@
         <v>80</v>
       </c>
       <c r="M35">
-        <v>0.6969</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="N35">
         <v>1610612746</v>
@@ -2543,7 +2543,7 @@
         <v>81</v>
       </c>
       <c r="M36">
-        <v>0.7739</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="N36">
         <v>1610612760</v>
@@ -2596,7 +2596,7 @@
         <v>81</v>
       </c>
       <c r="M37">
-        <v>0.7739</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="N37">
         <v>1610612760</v>
@@ -2649,7 +2649,7 @@
         <v>82</v>
       </c>
       <c r="M38">
-        <v>0.3731</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="N38">
         <v>1610612760</v>
@@ -2702,7 +2702,7 @@
         <v>82</v>
       </c>
       <c r="M39">
-        <v>0.3731</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="N39">
         <v>1610612760</v>
@@ -2755,7 +2755,7 @@
         <v>81</v>
       </c>
       <c r="M40">
-        <v>0.7739</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="N40">
         <v>1610612760</v>
@@ -2808,7 +2808,7 @@
         <v>82</v>
       </c>
       <c r="M41">
-        <v>0.3731</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="N41">
         <v>1610612760</v>
@@ -2861,7 +2861,7 @@
         <v>81</v>
       </c>
       <c r="M42">
-        <v>0.7739</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="N42">
         <v>1610612760</v>
@@ -2914,7 +2914,7 @@
         <v>79</v>
       </c>
       <c r="M43">
-        <v>0.7975</v>
+        <v>0.8098</v>
       </c>
       <c r="N43">
         <v>1610612759</v>
@@ -2967,7 +2967,7 @@
         <v>79</v>
       </c>
       <c r="M44">
-        <v>0.7975</v>
+        <v>0.8098</v>
       </c>
       <c r="N44">
         <v>1610612759</v>
@@ -3020,7 +3020,7 @@
         <v>83</v>
       </c>
       <c r="M45">
-        <v>0.3402</v>
+        <v>0.3089</v>
       </c>
       <c r="N45">
         <v>1610612759</v>
@@ -3073,7 +3073,7 @@
         <v>83</v>
       </c>
       <c r="M46">
-        <v>0.3402</v>
+        <v>0.3089</v>
       </c>
       <c r="N46">
         <v>1610612759</v>
@@ -3126,7 +3126,7 @@
         <v>79</v>
       </c>
       <c r="M47">
-        <v>0.7975</v>
+        <v>0.8098</v>
       </c>
       <c r="N47">
         <v>1610612759</v>
@@ -3179,7 +3179,7 @@
         <v>83</v>
       </c>
       <c r="M48">
-        <v>0.3402</v>
+        <v>0.3089</v>
       </c>
       <c r="N48">
         <v>1610612759</v>
@@ -3232,7 +3232,7 @@
         <v>79</v>
       </c>
       <c r="M49">
-        <v>0.7975</v>
+        <v>0.8098</v>
       </c>
       <c r="N49">
         <v>1610612759</v>
@@ -3285,7 +3285,7 @@
         <v>85</v>
       </c>
       <c r="M50">
-        <v>0.7121</v>
+        <v>0.7035</v>
       </c>
       <c r="N50">
         <v>1610612743</v>
@@ -3338,7 +3338,7 @@
         <v>85</v>
       </c>
       <c r="M51">
-        <v>0.7121</v>
+        <v>0.7035</v>
       </c>
       <c r="N51">
         <v>1610612743</v>
@@ -3391,7 +3391,7 @@
         <v>84</v>
       </c>
       <c r="M52">
-        <v>0.4264</v>
+        <v>0.4145</v>
       </c>
       <c r="N52">
         <v>1610612743</v>
@@ -3444,7 +3444,7 @@
         <v>84</v>
       </c>
       <c r="M53">
-        <v>0.4264</v>
+        <v>0.4145</v>
       </c>
       <c r="N53">
         <v>1610612743</v>
@@ -3497,7 +3497,7 @@
         <v>85</v>
       </c>
       <c r="M54">
-        <v>0.7121</v>
+        <v>0.7035</v>
       </c>
       <c r="N54">
         <v>1610612743</v>
@@ -3550,7 +3550,7 @@
         <v>84</v>
       </c>
       <c r="M55">
-        <v>0.4264</v>
+        <v>0.4145</v>
       </c>
       <c r="N55">
         <v>1610612743</v>
@@ -3603,7 +3603,7 @@
         <v>85</v>
       </c>
       <c r="M56">
-        <v>0.7121</v>
+        <v>0.7035</v>
       </c>
       <c r="N56">
         <v>1610612743</v>
@@ -3656,7 +3656,7 @@
         <v>87</v>
       </c>
       <c r="M57">
-        <v>0.4014</v>
+        <v>0.4086</v>
       </c>
       <c r="N57">
         <v>1610612747</v>
@@ -3709,7 +3709,7 @@
         <v>87</v>
       </c>
       <c r="M58">
-        <v>0.4014</v>
+        <v>0.4086</v>
       </c>
       <c r="N58">
         <v>1610612747</v>
@@ -3762,7 +3762,7 @@
         <v>86</v>
       </c>
       <c r="M59">
-        <v>0.7082000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="N59">
         <v>1610612747</v>
@@ -3815,7 +3815,7 @@
         <v>86</v>
       </c>
       <c r="M60">
-        <v>0.7082000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="N60">
         <v>1610612747</v>
@@ -3868,7 +3868,7 @@
         <v>87</v>
       </c>
       <c r="M61">
-        <v>0.4014</v>
+        <v>0.4086</v>
       </c>
       <c r="N61">
         <v>1610612747</v>
@@ -3921,7 +3921,7 @@
         <v>86</v>
       </c>
       <c r="M62">
-        <v>0.7082000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="N62">
         <v>1610612747</v>
@@ -3974,7 +3974,7 @@
         <v>87</v>
       </c>
       <c r="M63">
-        <v>0.4014</v>
+        <v>0.4086</v>
       </c>
       <c r="N63">
         <v>1610612747</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -172,15 +172,15 @@
     <t>2026-05-02</t>
   </si>
   <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
     <t>ORL</t>
   </si>
   <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
     <t>DET</t>
   </si>
   <si>
@@ -202,12 +202,12 @@
     <t>PHX</t>
   </si>
   <si>
+    <t>LAC</t>
+  </si>
+  <si>
     <t>POR</t>
   </si>
   <si>
-    <t>LAC</t>
-  </si>
-  <si>
     <t>OKC</t>
   </si>
   <si>
@@ -226,15 +226,15 @@
     <t>HOU</t>
   </si>
   <si>
+    <t>Philadelphia 76ers</t>
+  </si>
+  <si>
+    <t>Charlotte Hornets</t>
+  </si>
+  <si>
     <t>Orlando Magic</t>
   </si>
   <si>
-    <t>Charlotte Hornets</t>
-  </si>
-  <si>
-    <t>Philadelphia 76ers</t>
-  </si>
-  <si>
     <t>Detroit Pistons</t>
   </si>
   <si>
@@ -256,10 +256,10 @@
     <t>Phoenix Suns</t>
   </si>
   <si>
+    <t>LA Clippers</t>
+  </si>
+  <si>
     <t>Portland Trail Blazers</t>
-  </si>
-  <si>
-    <t>LA Clippers</t>
   </si>
   <si>
     <t>Oklahoma City Thunder</t>
@@ -723,7 +723,7 @@
         <v>175</v>
       </c>
       <c r="G2">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="H2" t="s">
         <v>52</v>
@@ -732,7 +732,7 @@
         <v>70</v>
       </c>
       <c r="J2">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="K2" t="s">
         <v>54</v>
@@ -741,13 +741,13 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>0.5609</v>
+        <v>0.5535</v>
       </c>
       <c r="N2">
+        <v>1610612755</v>
+      </c>
+      <c r="O2">
         <v>1610612753</v>
-      </c>
-      <c r="O2">
-        <v>1610612755</v>
       </c>
       <c r="P2">
         <v>7</v>
@@ -794,7 +794,7 @@
         <v>90</v>
       </c>
       <c r="M3">
-        <v>0.7012</v>
+        <v>0.6723</v>
       </c>
       <c r="N3">
         <v>1610612766</v>
@@ -829,7 +829,7 @@
         <v>178</v>
       </c>
       <c r="G4">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="H4" t="s">
         <v>54</v>
@@ -850,7 +850,7 @@
         <v>0.4403</v>
       </c>
       <c r="N4">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="O4">
         <v>1610612766</v>
@@ -891,7 +891,7 @@
         <v>73</v>
       </c>
       <c r="J5">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="K5" t="s">
         <v>54</v>
@@ -900,13 +900,13 @@
         <v>72</v>
       </c>
       <c r="M5">
-        <v>0.7683</v>
+        <v>0.7821</v>
       </c>
       <c r="N5">
         <v>1610612765</v>
       </c>
       <c r="O5">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P5">
         <v>1</v>
@@ -944,7 +944,7 @@
         <v>73</v>
       </c>
       <c r="J6">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="K6" t="s">
         <v>54</v>
@@ -953,13 +953,13 @@
         <v>72</v>
       </c>
       <c r="M6">
-        <v>0.7683</v>
+        <v>0.7821</v>
       </c>
       <c r="N6">
         <v>1610612765</v>
       </c>
       <c r="O6">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -988,7 +988,7 @@
         <v>184</v>
       </c>
       <c r="G7">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="H7" t="s">
         <v>54</v>
@@ -1006,13 +1006,13 @@
         <v>73</v>
       </c>
       <c r="M7">
-        <v>0.3751</v>
+        <v>0.3788</v>
       </c>
       <c r="N7">
         <v>1610612765</v>
       </c>
       <c r="O7">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P7">
         <v>1</v>
@@ -1041,7 +1041,7 @@
         <v>186</v>
       </c>
       <c r="G8">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="H8" t="s">
         <v>54</v>
@@ -1059,13 +1059,13 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>0.3751</v>
+        <v>0.3788</v>
       </c>
       <c r="N8">
         <v>1610612765</v>
       </c>
       <c r="O8">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P8">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>73</v>
       </c>
       <c r="J9">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="K9" t="s">
         <v>54</v>
@@ -1112,13 +1112,13 @@
         <v>72</v>
       </c>
       <c r="M9">
-        <v>0.7683</v>
+        <v>0.7821</v>
       </c>
       <c r="N9">
         <v>1610612765</v>
       </c>
       <c r="O9">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P9">
         <v>1</v>
@@ -1147,7 +1147,7 @@
         <v>190</v>
       </c>
       <c r="G10">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="H10" t="s">
         <v>54</v>
@@ -1165,13 +1165,13 @@
         <v>73</v>
       </c>
       <c r="M10">
-        <v>0.3751</v>
+        <v>0.3788</v>
       </c>
       <c r="N10">
         <v>1610612765</v>
       </c>
       <c r="O10">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1209,7 +1209,7 @@
         <v>73</v>
       </c>
       <c r="J11">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="K11" t="s">
         <v>54</v>
@@ -1218,13 +1218,13 @@
         <v>72</v>
       </c>
       <c r="M11">
-        <v>0.7683</v>
+        <v>0.7821</v>
       </c>
       <c r="N11">
         <v>1610612765</v>
       </c>
       <c r="O11">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -1262,7 +1262,7 @@
         <v>74</v>
       </c>
       <c r="J12">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="K12" t="s">
         <v>52</v>
@@ -1271,13 +1271,13 @@
         <v>70</v>
       </c>
       <c r="M12">
-        <v>0.8181</v>
+        <v>0.6916</v>
       </c>
       <c r="N12">
         <v>1610612738</v>
       </c>
       <c r="O12">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="P12">
         <v>2</v>
@@ -1315,7 +1315,7 @@
         <v>74</v>
       </c>
       <c r="J13">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="K13" t="s">
         <v>52</v>
@@ -1324,13 +1324,13 @@
         <v>70</v>
       </c>
       <c r="M13">
-        <v>0.8181</v>
+        <v>0.6916</v>
       </c>
       <c r="N13">
         <v>1610612738</v>
       </c>
       <c r="O13">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="P13">
         <v>2</v>
@@ -1359,7 +1359,7 @@
         <v>184</v>
       </c>
       <c r="G14">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="H14" t="s">
         <v>52</v>
@@ -1377,13 +1377,13 @@
         <v>74</v>
       </c>
       <c r="M14">
-        <v>0.3204</v>
+        <v>0.4888</v>
       </c>
       <c r="N14">
         <v>1610612738</v>
       </c>
       <c r="O14">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="P14">
         <v>2</v>
@@ -1412,7 +1412,7 @@
         <v>186</v>
       </c>
       <c r="G15">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="H15" t="s">
         <v>52</v>
@@ -1430,13 +1430,13 @@
         <v>74</v>
       </c>
       <c r="M15">
-        <v>0.3204</v>
+        <v>0.4888</v>
       </c>
       <c r="N15">
         <v>1610612738</v>
       </c>
       <c r="O15">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="P15">
         <v>2</v>
@@ -1474,7 +1474,7 @@
         <v>74</v>
       </c>
       <c r="J16">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="K16" t="s">
         <v>52</v>
@@ -1483,13 +1483,13 @@
         <v>70</v>
       </c>
       <c r="M16">
-        <v>0.8181</v>
+        <v>0.6916</v>
       </c>
       <c r="N16">
         <v>1610612738</v>
       </c>
       <c r="O16">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="P16">
         <v>2</v>
@@ -1518,7 +1518,7 @@
         <v>190</v>
       </c>
       <c r="G17">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="H17" t="s">
         <v>52</v>
@@ -1536,13 +1536,13 @@
         <v>74</v>
       </c>
       <c r="M17">
-        <v>0.3204</v>
+        <v>0.4888</v>
       </c>
       <c r="N17">
         <v>1610612738</v>
       </c>
       <c r="O17">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="P17">
         <v>2</v>
@@ -1580,7 +1580,7 @@
         <v>74</v>
       </c>
       <c r="J18">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="K18" t="s">
         <v>52</v>
@@ -1589,13 +1589,13 @@
         <v>70</v>
       </c>
       <c r="M18">
-        <v>0.8181</v>
+        <v>0.6916</v>
       </c>
       <c r="N18">
         <v>1610612738</v>
       </c>
       <c r="O18">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="P18">
         <v>2</v>
@@ -1642,7 +1642,7 @@
         <v>76</v>
       </c>
       <c r="M19">
-        <v>0.7002</v>
+        <v>0.6041</v>
       </c>
       <c r="N19">
         <v>1610612752</v>
@@ -1695,7 +1695,7 @@
         <v>76</v>
       </c>
       <c r="M20">
-        <v>0.7002</v>
+        <v>0.6041</v>
       </c>
       <c r="N20">
         <v>1610612752</v>
@@ -1748,7 +1748,7 @@
         <v>75</v>
       </c>
       <c r="M21">
-        <v>0.4653</v>
+        <v>0.6142</v>
       </c>
       <c r="N21">
         <v>1610612752</v>
@@ -1801,7 +1801,7 @@
         <v>75</v>
       </c>
       <c r="M22">
-        <v>0.4653</v>
+        <v>0.6142</v>
       </c>
       <c r="N22">
         <v>1610612752</v>
@@ -1854,7 +1854,7 @@
         <v>76</v>
       </c>
       <c r="M23">
-        <v>0.7002</v>
+        <v>0.6041</v>
       </c>
       <c r="N23">
         <v>1610612752</v>
@@ -1907,7 +1907,7 @@
         <v>75</v>
       </c>
       <c r="M24">
-        <v>0.4653</v>
+        <v>0.6142</v>
       </c>
       <c r="N24">
         <v>1610612752</v>
@@ -1960,7 +1960,7 @@
         <v>76</v>
       </c>
       <c r="M25">
-        <v>0.7002</v>
+        <v>0.6041</v>
       </c>
       <c r="N25">
         <v>1610612752</v>
@@ -2013,7 +2013,7 @@
         <v>78</v>
       </c>
       <c r="M26">
-        <v>0.5843</v>
+        <v>0.5327</v>
       </c>
       <c r="N26">
         <v>1610612739</v>
@@ -2066,7 +2066,7 @@
         <v>78</v>
       </c>
       <c r="M27">
-        <v>0.5843</v>
+        <v>0.5327</v>
       </c>
       <c r="N27">
         <v>1610612739</v>
@@ -2119,7 +2119,7 @@
         <v>77</v>
       </c>
       <c r="M28">
-        <v>0.5152</v>
+        <v>0.6518</v>
       </c>
       <c r="N28">
         <v>1610612739</v>
@@ -2172,7 +2172,7 @@
         <v>77</v>
       </c>
       <c r="M29">
-        <v>0.5152</v>
+        <v>0.6518</v>
       </c>
       <c r="N29">
         <v>1610612739</v>
@@ -2225,7 +2225,7 @@
         <v>78</v>
       </c>
       <c r="M30">
-        <v>0.5843</v>
+        <v>0.5327</v>
       </c>
       <c r="N30">
         <v>1610612739</v>
@@ -2278,7 +2278,7 @@
         <v>77</v>
       </c>
       <c r="M31">
-        <v>0.5152</v>
+        <v>0.6518</v>
       </c>
       <c r="N31">
         <v>1610612739</v>
@@ -2331,7 +2331,7 @@
         <v>78</v>
       </c>
       <c r="M32">
-        <v>0.5843</v>
+        <v>0.5327</v>
       </c>
       <c r="N32">
         <v>1610612739</v>
@@ -2375,7 +2375,7 @@
         <v>79</v>
       </c>
       <c r="J33">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K33" t="s">
         <v>63</v>
@@ -2384,13 +2384,13 @@
         <v>81</v>
       </c>
       <c r="M33">
-        <v>0.4634</v>
+        <v>0.5828</v>
       </c>
       <c r="N33">
         <v>1610612756</v>
       </c>
       <c r="O33">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P33">
         <v>7</v>
@@ -2419,7 +2419,7 @@
         <v>176</v>
       </c>
       <c r="G34">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="H34" t="s">
         <v>62</v>
@@ -2437,10 +2437,10 @@
         <v>91</v>
       </c>
       <c r="M34">
-        <v>0.5741000000000001</v>
+        <v>0.6619</v>
       </c>
       <c r="N34">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="O34">
         <v>1610612744</v>
@@ -2472,7 +2472,7 @@
         <v>178</v>
       </c>
       <c r="G35">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="H35" t="s">
         <v>63</v>
@@ -2481,7 +2481,7 @@
         <v>81</v>
       </c>
       <c r="J35">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="K35" t="s">
         <v>62</v>
@@ -2490,13 +2490,13 @@
         <v>80</v>
       </c>
       <c r="M35">
-        <v>0.6991000000000001</v>
+        <v>0.508</v>
       </c>
       <c r="N35">
+        <v>1610612757</v>
+      </c>
+      <c r="O35">
         <v>1610612746</v>
-      </c>
-      <c r="O35">
-        <v>1610612757</v>
       </c>
       <c r="P35">
         <v>8</v>
@@ -2534,7 +2534,7 @@
         <v>82</v>
       </c>
       <c r="J36">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K36" t="s">
         <v>63</v>
@@ -2543,13 +2543,13 @@
         <v>81</v>
       </c>
       <c r="M36">
-        <v>0.6477000000000001</v>
+        <v>0.6296</v>
       </c>
       <c r="N36">
         <v>1610612760</v>
       </c>
       <c r="O36">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P36">
         <v>1</v>
@@ -2587,7 +2587,7 @@
         <v>82</v>
       </c>
       <c r="J37">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K37" t="s">
         <v>63</v>
@@ -2596,13 +2596,13 @@
         <v>81</v>
       </c>
       <c r="M37">
-        <v>0.6477000000000001</v>
+        <v>0.6296</v>
       </c>
       <c r="N37">
         <v>1610612760</v>
       </c>
       <c r="O37">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P37">
         <v>1</v>
@@ -2631,7 +2631,7 @@
         <v>185</v>
       </c>
       <c r="G38">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="H38" t="s">
         <v>63</v>
@@ -2649,13 +2649,13 @@
         <v>82</v>
       </c>
       <c r="M38">
-        <v>0.5276999999999999</v>
+        <v>0.4492</v>
       </c>
       <c r="N38">
         <v>1610612760</v>
       </c>
       <c r="O38">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P38">
         <v>1</v>
@@ -2684,7 +2684,7 @@
         <v>187</v>
       </c>
       <c r="G39">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="H39" t="s">
         <v>63</v>
@@ -2702,13 +2702,13 @@
         <v>82</v>
       </c>
       <c r="M39">
-        <v>0.5276999999999999</v>
+        <v>0.4492</v>
       </c>
       <c r="N39">
         <v>1610612760</v>
       </c>
       <c r="O39">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P39">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>82</v>
       </c>
       <c r="J40">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K40" t="s">
         <v>63</v>
@@ -2755,13 +2755,13 @@
         <v>81</v>
       </c>
       <c r="M40">
-        <v>0.6477000000000001</v>
+        <v>0.6296</v>
       </c>
       <c r="N40">
         <v>1610612760</v>
       </c>
       <c r="O40">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P40">
         <v>1</v>
@@ -2790,7 +2790,7 @@
         <v>191</v>
       </c>
       <c r="G41">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="H41" t="s">
         <v>63</v>
@@ -2808,13 +2808,13 @@
         <v>82</v>
       </c>
       <c r="M41">
-        <v>0.5276999999999999</v>
+        <v>0.4492</v>
       </c>
       <c r="N41">
         <v>1610612760</v>
       </c>
       <c r="O41">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P41">
         <v>1</v>
@@ -2852,7 +2852,7 @@
         <v>82</v>
       </c>
       <c r="J42">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="K42" t="s">
         <v>63</v>
@@ -2861,13 +2861,13 @@
         <v>81</v>
       </c>
       <c r="M42">
-        <v>0.6477000000000001</v>
+        <v>0.6296</v>
       </c>
       <c r="N42">
         <v>1610612760</v>
       </c>
       <c r="O42">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="P42">
         <v>1</v>
@@ -2914,7 +2914,7 @@
         <v>79</v>
       </c>
       <c r="M43">
-        <v>0.8098</v>
+        <v>0.7287</v>
       </c>
       <c r="N43">
         <v>1610612759</v>
@@ -2967,7 +2967,7 @@
         <v>79</v>
       </c>
       <c r="M44">
-        <v>0.8098</v>
+        <v>0.7287</v>
       </c>
       <c r="N44">
         <v>1610612759</v>
@@ -3020,7 +3020,7 @@
         <v>83</v>
       </c>
       <c r="M45">
-        <v>0.3089</v>
+        <v>0.3835</v>
       </c>
       <c r="N45">
         <v>1610612759</v>
@@ -3073,7 +3073,7 @@
         <v>83</v>
       </c>
       <c r="M46">
-        <v>0.3089</v>
+        <v>0.3835</v>
       </c>
       <c r="N46">
         <v>1610612759</v>
@@ -3126,7 +3126,7 @@
         <v>79</v>
       </c>
       <c r="M47">
-        <v>0.8098</v>
+        <v>0.7287</v>
       </c>
       <c r="N47">
         <v>1610612759</v>
@@ -3179,7 +3179,7 @@
         <v>83</v>
       </c>
       <c r="M48">
-        <v>0.3089</v>
+        <v>0.3835</v>
       </c>
       <c r="N48">
         <v>1610612759</v>
@@ -3232,7 +3232,7 @@
         <v>79</v>
       </c>
       <c r="M49">
-        <v>0.8098</v>
+        <v>0.7287</v>
       </c>
       <c r="N49">
         <v>1610612759</v>
@@ -3285,7 +3285,7 @@
         <v>85</v>
       </c>
       <c r="M50">
-        <v>0.7035</v>
+        <v>0.722</v>
       </c>
       <c r="N50">
         <v>1610612743</v>
@@ -3338,7 +3338,7 @@
         <v>85</v>
       </c>
       <c r="M51">
-        <v>0.7035</v>
+        <v>0.722</v>
       </c>
       <c r="N51">
         <v>1610612743</v>
@@ -3391,7 +3391,7 @@
         <v>84</v>
       </c>
       <c r="M52">
-        <v>0.4145</v>
+        <v>0.4046</v>
       </c>
       <c r="N52">
         <v>1610612743</v>
@@ -3444,7 +3444,7 @@
         <v>84</v>
       </c>
       <c r="M53">
-        <v>0.4145</v>
+        <v>0.4046</v>
       </c>
       <c r="N53">
         <v>1610612743</v>
@@ -3497,7 +3497,7 @@
         <v>85</v>
       </c>
       <c r="M54">
-        <v>0.7035</v>
+        <v>0.722</v>
       </c>
       <c r="N54">
         <v>1610612743</v>
@@ -3550,7 +3550,7 @@
         <v>84</v>
       </c>
       <c r="M55">
-        <v>0.4145</v>
+        <v>0.4046</v>
       </c>
       <c r="N55">
         <v>1610612743</v>
@@ -3603,7 +3603,7 @@
         <v>85</v>
       </c>
       <c r="M56">
-        <v>0.7035</v>
+        <v>0.722</v>
       </c>
       <c r="N56">
         <v>1610612743</v>
@@ -3656,7 +3656,7 @@
         <v>87</v>
       </c>
       <c r="M57">
-        <v>0.4086</v>
+        <v>0.5391</v>
       </c>
       <c r="N57">
         <v>1610612747</v>
@@ -3709,7 +3709,7 @@
         <v>87</v>
       </c>
       <c r="M58">
-        <v>0.4086</v>
+        <v>0.5391</v>
       </c>
       <c r="N58">
         <v>1610612747</v>
@@ -3762,7 +3762,7 @@
         <v>86</v>
       </c>
       <c r="M59">
-        <v>0.695</v>
+        <v>0.5802</v>
       </c>
       <c r="N59">
         <v>1610612747</v>
@@ -3815,7 +3815,7 @@
         <v>86</v>
       </c>
       <c r="M60">
-        <v>0.695</v>
+        <v>0.5802</v>
       </c>
       <c r="N60">
         <v>1610612747</v>
@@ -3868,7 +3868,7 @@
         <v>87</v>
       </c>
       <c r="M61">
-        <v>0.4086</v>
+        <v>0.5391</v>
       </c>
       <c r="N61">
         <v>1610612747</v>
@@ -3921,7 +3921,7 @@
         <v>86</v>
       </c>
       <c r="M62">
-        <v>0.695</v>
+        <v>0.5802</v>
       </c>
       <c r="N62">
         <v>1610612747</v>
@@ -3974,7 +3974,7 @@
         <v>87</v>
       </c>
       <c r="M63">
-        <v>0.4086</v>
+        <v>0.5391</v>
       </c>
       <c r="N63">
         <v>1610612747</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -741,7 +741,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>0.5535</v>
+        <v>0.5474</v>
       </c>
       <c r="N2">
         <v>1610612755</v>
@@ -794,7 +794,7 @@
         <v>90</v>
       </c>
       <c r="M3">
-        <v>0.6723</v>
+        <v>0.6625</v>
       </c>
       <c r="N3">
         <v>1610612766</v>
@@ -847,7 +847,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>0.4403</v>
+        <v>0.4904</v>
       </c>
       <c r="N4">
         <v>1610612753</v>
@@ -900,7 +900,7 @@
         <v>72</v>
       </c>
       <c r="M5">
-        <v>0.7821</v>
+        <v>0.7502</v>
       </c>
       <c r="N5">
         <v>1610612765</v>
@@ -953,7 +953,7 @@
         <v>72</v>
       </c>
       <c r="M6">
-        <v>0.7821</v>
+        <v>0.7502</v>
       </c>
       <c r="N6">
         <v>1610612765</v>
@@ -1006,7 +1006,7 @@
         <v>73</v>
       </c>
       <c r="M7">
-        <v>0.3788</v>
+        <v>0.3865</v>
       </c>
       <c r="N7">
         <v>1610612765</v>
@@ -1059,7 +1059,7 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>0.3788</v>
+        <v>0.3865</v>
       </c>
       <c r="N8">
         <v>1610612765</v>
@@ -1112,7 +1112,7 @@
         <v>72</v>
       </c>
       <c r="M9">
-        <v>0.7821</v>
+        <v>0.7502</v>
       </c>
       <c r="N9">
         <v>1610612765</v>
@@ -1165,7 +1165,7 @@
         <v>73</v>
       </c>
       <c r="M10">
-        <v>0.3788</v>
+        <v>0.3865</v>
       </c>
       <c r="N10">
         <v>1610612765</v>
@@ -1218,7 +1218,7 @@
         <v>72</v>
       </c>
       <c r="M11">
-        <v>0.7821</v>
+        <v>0.7502</v>
       </c>
       <c r="N11">
         <v>1610612765</v>
@@ -1271,7 +1271,7 @@
         <v>70</v>
       </c>
       <c r="M12">
-        <v>0.6916</v>
+        <v>0.7841</v>
       </c>
       <c r="N12">
         <v>1610612738</v>
@@ -1324,7 +1324,7 @@
         <v>70</v>
       </c>
       <c r="M13">
-        <v>0.6916</v>
+        <v>0.7841</v>
       </c>
       <c r="N13">
         <v>1610612738</v>
@@ -1377,7 +1377,7 @@
         <v>74</v>
       </c>
       <c r="M14">
-        <v>0.4888</v>
+        <v>0.3553</v>
       </c>
       <c r="N14">
         <v>1610612738</v>
@@ -1430,7 +1430,7 @@
         <v>74</v>
       </c>
       <c r="M15">
-        <v>0.4888</v>
+        <v>0.3553</v>
       </c>
       <c r="N15">
         <v>1610612738</v>
@@ -1483,7 +1483,7 @@
         <v>70</v>
       </c>
       <c r="M16">
-        <v>0.6916</v>
+        <v>0.7841</v>
       </c>
       <c r="N16">
         <v>1610612738</v>
@@ -1536,7 +1536,7 @@
         <v>74</v>
       </c>
       <c r="M17">
-        <v>0.4888</v>
+        <v>0.3553</v>
       </c>
       <c r="N17">
         <v>1610612738</v>
@@ -1589,7 +1589,7 @@
         <v>70</v>
       </c>
       <c r="M18">
-        <v>0.6916</v>
+        <v>0.7841</v>
       </c>
       <c r="N18">
         <v>1610612738</v>
@@ -1642,7 +1642,7 @@
         <v>76</v>
       </c>
       <c r="M19">
-        <v>0.6041</v>
+        <v>0.7046</v>
       </c>
       <c r="N19">
         <v>1610612752</v>
@@ -1695,7 +1695,7 @@
         <v>76</v>
       </c>
       <c r="M20">
-        <v>0.6041</v>
+        <v>0.7046</v>
       </c>
       <c r="N20">
         <v>1610612752</v>
@@ -1748,7 +1748,7 @@
         <v>75</v>
       </c>
       <c r="M21">
-        <v>0.6142</v>
+        <v>0.4876</v>
       </c>
       <c r="N21">
         <v>1610612752</v>
@@ -1801,7 +1801,7 @@
         <v>75</v>
       </c>
       <c r="M22">
-        <v>0.6142</v>
+        <v>0.4876</v>
       </c>
       <c r="N22">
         <v>1610612752</v>
@@ -1854,7 +1854,7 @@
         <v>76</v>
       </c>
       <c r="M23">
-        <v>0.6041</v>
+        <v>0.7046</v>
       </c>
       <c r="N23">
         <v>1610612752</v>
@@ -1907,7 +1907,7 @@
         <v>75</v>
       </c>
       <c r="M24">
-        <v>0.6142</v>
+        <v>0.4876</v>
       </c>
       <c r="N24">
         <v>1610612752</v>
@@ -1960,7 +1960,7 @@
         <v>76</v>
       </c>
       <c r="M25">
-        <v>0.6041</v>
+        <v>0.7046</v>
       </c>
       <c r="N25">
         <v>1610612752</v>
@@ -2013,7 +2013,7 @@
         <v>78</v>
       </c>
       <c r="M26">
-        <v>0.5327</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="N26">
         <v>1610612739</v>
@@ -2066,7 +2066,7 @@
         <v>78</v>
       </c>
       <c r="M27">
-        <v>0.5327</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="N27">
         <v>1610612739</v>
@@ -2119,7 +2119,7 @@
         <v>77</v>
       </c>
       <c r="M28">
-        <v>0.6518</v>
+        <v>0.4711</v>
       </c>
       <c r="N28">
         <v>1610612739</v>
@@ -2172,7 +2172,7 @@
         <v>77</v>
       </c>
       <c r="M29">
-        <v>0.6518</v>
+        <v>0.4711</v>
       </c>
       <c r="N29">
         <v>1610612739</v>
@@ -2225,7 +2225,7 @@
         <v>78</v>
       </c>
       <c r="M30">
-        <v>0.5327</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="N30">
         <v>1610612739</v>
@@ -2278,7 +2278,7 @@
         <v>77</v>
       </c>
       <c r="M31">
-        <v>0.6518</v>
+        <v>0.4711</v>
       </c>
       <c r="N31">
         <v>1610612739</v>
@@ -2331,7 +2331,7 @@
         <v>78</v>
       </c>
       <c r="M32">
-        <v>0.5327</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="N32">
         <v>1610612739</v>
@@ -2384,7 +2384,7 @@
         <v>81</v>
       </c>
       <c r="M33">
-        <v>0.5828</v>
+        <v>0.5698</v>
       </c>
       <c r="N33">
         <v>1610612756</v>
@@ -2437,7 +2437,7 @@
         <v>91</v>
       </c>
       <c r="M34">
-        <v>0.6619</v>
+        <v>0.6486</v>
       </c>
       <c r="N34">
         <v>1610612746</v>
@@ -2490,7 +2490,7 @@
         <v>80</v>
       </c>
       <c r="M35">
-        <v>0.508</v>
+        <v>0.541</v>
       </c>
       <c r="N35">
         <v>1610612757</v>
@@ -2543,7 +2543,7 @@
         <v>81</v>
       </c>
       <c r="M36">
-        <v>0.6296</v>
+        <v>0.6298</v>
       </c>
       <c r="N36">
         <v>1610612760</v>
@@ -2596,7 +2596,7 @@
         <v>81</v>
       </c>
       <c r="M37">
-        <v>0.6296</v>
+        <v>0.6298</v>
       </c>
       <c r="N37">
         <v>1610612760</v>
@@ -2649,7 +2649,7 @@
         <v>82</v>
       </c>
       <c r="M38">
-        <v>0.4492</v>
+        <v>0.446</v>
       </c>
       <c r="N38">
         <v>1610612760</v>
@@ -2702,7 +2702,7 @@
         <v>82</v>
       </c>
       <c r="M39">
-        <v>0.4492</v>
+        <v>0.446</v>
       </c>
       <c r="N39">
         <v>1610612760</v>
@@ -2755,7 +2755,7 @@
         <v>81</v>
       </c>
       <c r="M40">
-        <v>0.6296</v>
+        <v>0.6298</v>
       </c>
       <c r="N40">
         <v>1610612760</v>
@@ -2808,7 +2808,7 @@
         <v>82</v>
       </c>
       <c r="M41">
-        <v>0.4492</v>
+        <v>0.446</v>
       </c>
       <c r="N41">
         <v>1610612760</v>
@@ -2861,7 +2861,7 @@
         <v>81</v>
       </c>
       <c r="M42">
-        <v>0.6296</v>
+        <v>0.6298</v>
       </c>
       <c r="N42">
         <v>1610612760</v>
@@ -2914,7 +2914,7 @@
         <v>79</v>
       </c>
       <c r="M43">
-        <v>0.7287</v>
+        <v>0.7333</v>
       </c>
       <c r="N43">
         <v>1610612759</v>
@@ -2967,7 +2967,7 @@
         <v>79</v>
       </c>
       <c r="M44">
-        <v>0.7287</v>
+        <v>0.7333</v>
       </c>
       <c r="N44">
         <v>1610612759</v>
@@ -3020,7 +3020,7 @@
         <v>83</v>
       </c>
       <c r="M45">
-        <v>0.3835</v>
+        <v>0.3895</v>
       </c>
       <c r="N45">
         <v>1610612759</v>
@@ -3073,7 +3073,7 @@
         <v>83</v>
       </c>
       <c r="M46">
-        <v>0.3835</v>
+        <v>0.3895</v>
       </c>
       <c r="N46">
         <v>1610612759</v>
@@ -3126,7 +3126,7 @@
         <v>79</v>
       </c>
       <c r="M47">
-        <v>0.7287</v>
+        <v>0.7333</v>
       </c>
       <c r="N47">
         <v>1610612759</v>
@@ -3179,7 +3179,7 @@
         <v>83</v>
       </c>
       <c r="M48">
-        <v>0.3835</v>
+        <v>0.3895</v>
       </c>
       <c r="N48">
         <v>1610612759</v>
@@ -3232,7 +3232,7 @@
         <v>79</v>
       </c>
       <c r="M49">
-        <v>0.7287</v>
+        <v>0.7333</v>
       </c>
       <c r="N49">
         <v>1610612759</v>
@@ -3285,7 +3285,7 @@
         <v>85</v>
       </c>
       <c r="M50">
-        <v>0.722</v>
+        <v>0.7055</v>
       </c>
       <c r="N50">
         <v>1610612743</v>
@@ -3338,7 +3338,7 @@
         <v>85</v>
       </c>
       <c r="M51">
-        <v>0.722</v>
+        <v>0.7055</v>
       </c>
       <c r="N51">
         <v>1610612743</v>
@@ -3391,7 +3391,7 @@
         <v>84</v>
       </c>
       <c r="M52">
-        <v>0.4046</v>
+        <v>0.427</v>
       </c>
       <c r="N52">
         <v>1610612743</v>
@@ -3444,7 +3444,7 @@
         <v>84</v>
       </c>
       <c r="M53">
-        <v>0.4046</v>
+        <v>0.427</v>
       </c>
       <c r="N53">
         <v>1610612743</v>
@@ -3497,7 +3497,7 @@
         <v>85</v>
       </c>
       <c r="M54">
-        <v>0.722</v>
+        <v>0.7055</v>
       </c>
       <c r="N54">
         <v>1610612743</v>
@@ -3550,7 +3550,7 @@
         <v>84</v>
       </c>
       <c r="M55">
-        <v>0.4046</v>
+        <v>0.427</v>
       </c>
       <c r="N55">
         <v>1610612743</v>
@@ -3603,7 +3603,7 @@
         <v>85</v>
       </c>
       <c r="M56">
-        <v>0.722</v>
+        <v>0.7055</v>
       </c>
       <c r="N56">
         <v>1610612743</v>
@@ -3656,7 +3656,7 @@
         <v>87</v>
       </c>
       <c r="M57">
-        <v>0.5391</v>
+        <v>0.4704</v>
       </c>
       <c r="N57">
         <v>1610612747</v>
@@ -3709,7 +3709,7 @@
         <v>87</v>
       </c>
       <c r="M58">
-        <v>0.5391</v>
+        <v>0.4704</v>
       </c>
       <c r="N58">
         <v>1610612747</v>
@@ -3762,7 +3762,7 @@
         <v>86</v>
       </c>
       <c r="M59">
-        <v>0.5802</v>
+        <v>0.6264</v>
       </c>
       <c r="N59">
         <v>1610612747</v>
@@ -3815,7 +3815,7 @@
         <v>86</v>
       </c>
       <c r="M60">
-        <v>0.5802</v>
+        <v>0.6264</v>
       </c>
       <c r="N60">
         <v>1610612747</v>
@@ -3868,7 +3868,7 @@
         <v>87</v>
       </c>
       <c r="M61">
-        <v>0.5391</v>
+        <v>0.4704</v>
       </c>
       <c r="N61">
         <v>1610612747</v>
@@ -3921,7 +3921,7 @@
         <v>86</v>
       </c>
       <c r="M62">
-        <v>0.5802</v>
+        <v>0.6264</v>
       </c>
       <c r="N62">
         <v>1610612747</v>
@@ -3974,7 +3974,7 @@
         <v>87</v>
       </c>
       <c r="M63">
-        <v>0.5391</v>
+        <v>0.4704</v>
       </c>
       <c r="N63">
         <v>1610612747</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -741,7 +741,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>0.5474</v>
+        <v>0.5542</v>
       </c>
       <c r="N2">
         <v>1610612755</v>
@@ -847,7 +847,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>0.4904</v>
+        <v>0.4848</v>
       </c>
       <c r="N4">
         <v>1610612753</v>
@@ -900,7 +900,7 @@
         <v>72</v>
       </c>
       <c r="M5">
-        <v>0.7502</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="N5">
         <v>1610612765</v>
@@ -953,7 +953,7 @@
         <v>72</v>
       </c>
       <c r="M6">
-        <v>0.7502</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="N6">
         <v>1610612765</v>
@@ -1006,7 +1006,7 @@
         <v>73</v>
       </c>
       <c r="M7">
-        <v>0.3865</v>
+        <v>0.3861</v>
       </c>
       <c r="N7">
         <v>1610612765</v>
@@ -1059,7 +1059,7 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>0.3865</v>
+        <v>0.3861</v>
       </c>
       <c r="N8">
         <v>1610612765</v>
@@ -1112,7 +1112,7 @@
         <v>72</v>
       </c>
       <c r="M9">
-        <v>0.7502</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="N9">
         <v>1610612765</v>
@@ -1165,7 +1165,7 @@
         <v>73</v>
       </c>
       <c r="M10">
-        <v>0.3865</v>
+        <v>0.3861</v>
       </c>
       <c r="N10">
         <v>1610612765</v>
@@ -1218,7 +1218,7 @@
         <v>72</v>
       </c>
       <c r="M11">
-        <v>0.7502</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="N11">
         <v>1610612765</v>
@@ -1377,7 +1377,7 @@
         <v>74</v>
       </c>
       <c r="M14">
-        <v>0.3553</v>
+        <v>0.3597</v>
       </c>
       <c r="N14">
         <v>1610612738</v>
@@ -1430,7 +1430,7 @@
         <v>74</v>
       </c>
       <c r="M15">
-        <v>0.3553</v>
+        <v>0.3597</v>
       </c>
       <c r="N15">
         <v>1610612738</v>
@@ -1536,7 +1536,7 @@
         <v>74</v>
       </c>
       <c r="M17">
-        <v>0.3553</v>
+        <v>0.3597</v>
       </c>
       <c r="N17">
         <v>1610612738</v>
@@ -2013,7 +2013,7 @@
         <v>78</v>
       </c>
       <c r="M26">
-        <v>0.7082000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="N26">
         <v>1610612739</v>
@@ -2066,7 +2066,7 @@
         <v>78</v>
       </c>
       <c r="M27">
-        <v>0.7082000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="N27">
         <v>1610612739</v>
@@ -2119,7 +2119,7 @@
         <v>77</v>
       </c>
       <c r="M28">
-        <v>0.4711</v>
+        <v>0.4648</v>
       </c>
       <c r="N28">
         <v>1610612739</v>
@@ -2172,7 +2172,7 @@
         <v>77</v>
       </c>
       <c r="M29">
-        <v>0.4711</v>
+        <v>0.4648</v>
       </c>
       <c r="N29">
         <v>1610612739</v>
@@ -2225,7 +2225,7 @@
         <v>78</v>
       </c>
       <c r="M30">
-        <v>0.7082000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="N30">
         <v>1610612739</v>
@@ -2278,7 +2278,7 @@
         <v>77</v>
       </c>
       <c r="M31">
-        <v>0.4711</v>
+        <v>0.4648</v>
       </c>
       <c r="N31">
         <v>1610612739</v>
@@ -2331,7 +2331,7 @@
         <v>78</v>
       </c>
       <c r="M32">
-        <v>0.7082000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="N32">
         <v>1610612739</v>
@@ -2384,7 +2384,7 @@
         <v>81</v>
       </c>
       <c r="M33">
-        <v>0.5698</v>
+        <v>0.5914</v>
       </c>
       <c r="N33">
         <v>1610612756</v>
@@ -2437,7 +2437,7 @@
         <v>91</v>
       </c>
       <c r="M34">
-        <v>0.6486</v>
+        <v>0.6475</v>
       </c>
       <c r="N34">
         <v>1610612746</v>
@@ -2490,7 +2490,7 @@
         <v>80</v>
       </c>
       <c r="M35">
-        <v>0.541</v>
+        <v>0.5315</v>
       </c>
       <c r="N35">
         <v>1610612757</v>
@@ -2543,7 +2543,7 @@
         <v>81</v>
       </c>
       <c r="M36">
-        <v>0.6298</v>
+        <v>0.6456</v>
       </c>
       <c r="N36">
         <v>1610612760</v>
@@ -2596,7 +2596,7 @@
         <v>81</v>
       </c>
       <c r="M37">
-        <v>0.6298</v>
+        <v>0.6456</v>
       </c>
       <c r="N37">
         <v>1610612760</v>
@@ -2649,7 +2649,7 @@
         <v>82</v>
       </c>
       <c r="M38">
-        <v>0.446</v>
+        <v>0.4232</v>
       </c>
       <c r="N38">
         <v>1610612760</v>
@@ -2702,7 +2702,7 @@
         <v>82</v>
       </c>
       <c r="M39">
-        <v>0.446</v>
+        <v>0.4232</v>
       </c>
       <c r="N39">
         <v>1610612760</v>
@@ -2755,7 +2755,7 @@
         <v>81</v>
       </c>
       <c r="M40">
-        <v>0.6298</v>
+        <v>0.6456</v>
       </c>
       <c r="N40">
         <v>1610612760</v>
@@ -2808,7 +2808,7 @@
         <v>82</v>
       </c>
       <c r="M41">
-        <v>0.446</v>
+        <v>0.4232</v>
       </c>
       <c r="N41">
         <v>1610612760</v>
@@ -2861,7 +2861,7 @@
         <v>81</v>
       </c>
       <c r="M42">
-        <v>0.6298</v>
+        <v>0.6456</v>
       </c>
       <c r="N42">
         <v>1610612760</v>
@@ -3391,7 +3391,7 @@
         <v>84</v>
       </c>
       <c r="M52">
-        <v>0.427</v>
+        <v>0.4217</v>
       </c>
       <c r="N52">
         <v>1610612743</v>
@@ -3444,7 +3444,7 @@
         <v>84</v>
       </c>
       <c r="M53">
-        <v>0.427</v>
+        <v>0.4217</v>
       </c>
       <c r="N53">
         <v>1610612743</v>
@@ -3550,7 +3550,7 @@
         <v>84</v>
       </c>
       <c r="M55">
-        <v>0.427</v>
+        <v>0.4217</v>
       </c>
       <c r="N55">
         <v>1610612743</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -741,7 +741,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>0.5542</v>
+        <v>0.5129</v>
       </c>
       <c r="N2">
         <v>1610612755</v>
@@ -794,7 +794,7 @@
         <v>90</v>
       </c>
       <c r="M3">
-        <v>0.6625</v>
+        <v>0.6605</v>
       </c>
       <c r="N3">
         <v>1610612766</v>
@@ -847,7 +847,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>0.4848</v>
+        <v>0.5075</v>
       </c>
       <c r="N4">
         <v>1610612753</v>
@@ -900,7 +900,7 @@
         <v>72</v>
       </c>
       <c r="M5">
-        <v>0.7625999999999999</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N5">
         <v>1610612765</v>
@@ -953,7 +953,7 @@
         <v>72</v>
       </c>
       <c r="M6">
-        <v>0.7625999999999999</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N6">
         <v>1610612765</v>
@@ -1006,7 +1006,7 @@
         <v>73</v>
       </c>
       <c r="M7">
-        <v>0.3861</v>
+        <v>0.3871</v>
       </c>
       <c r="N7">
         <v>1610612765</v>
@@ -1059,7 +1059,7 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>0.3861</v>
+        <v>0.3871</v>
       </c>
       <c r="N8">
         <v>1610612765</v>
@@ -1112,7 +1112,7 @@
         <v>72</v>
       </c>
       <c r="M9">
-        <v>0.7625999999999999</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N9">
         <v>1610612765</v>
@@ -1165,7 +1165,7 @@
         <v>73</v>
       </c>
       <c r="M10">
-        <v>0.3861</v>
+        <v>0.3871</v>
       </c>
       <c r="N10">
         <v>1610612765</v>
@@ -1218,7 +1218,7 @@
         <v>72</v>
       </c>
       <c r="M11">
-        <v>0.7625999999999999</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N11">
         <v>1610612765</v>
@@ -1271,7 +1271,7 @@
         <v>70</v>
       </c>
       <c r="M12">
-        <v>0.7841</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N12">
         <v>1610612738</v>
@@ -1324,7 +1324,7 @@
         <v>70</v>
       </c>
       <c r="M13">
-        <v>0.7841</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N13">
         <v>1610612738</v>
@@ -1377,7 +1377,7 @@
         <v>74</v>
       </c>
       <c r="M14">
-        <v>0.3597</v>
+        <v>0.3263</v>
       </c>
       <c r="N14">
         <v>1610612738</v>
@@ -1430,7 +1430,7 @@
         <v>74</v>
       </c>
       <c r="M15">
-        <v>0.3597</v>
+        <v>0.3263</v>
       </c>
       <c r="N15">
         <v>1610612738</v>
@@ -1483,7 +1483,7 @@
         <v>70</v>
       </c>
       <c r="M16">
-        <v>0.7841</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N16">
         <v>1610612738</v>
@@ -1536,7 +1536,7 @@
         <v>74</v>
       </c>
       <c r="M17">
-        <v>0.3597</v>
+        <v>0.3263</v>
       </c>
       <c r="N17">
         <v>1610612738</v>
@@ -1589,7 +1589,7 @@
         <v>70</v>
       </c>
       <c r="M18">
-        <v>0.7841</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N18">
         <v>1610612738</v>
@@ -1642,7 +1642,7 @@
         <v>76</v>
       </c>
       <c r="M19">
-        <v>0.7046</v>
+        <v>0.7078</v>
       </c>
       <c r="N19">
         <v>1610612752</v>
@@ -1695,7 +1695,7 @@
         <v>76</v>
       </c>
       <c r="M20">
-        <v>0.7046</v>
+        <v>0.7078</v>
       </c>
       <c r="N20">
         <v>1610612752</v>
@@ -1748,7 +1748,7 @@
         <v>75</v>
       </c>
       <c r="M21">
-        <v>0.4876</v>
+        <v>0.4757</v>
       </c>
       <c r="N21">
         <v>1610612752</v>
@@ -1801,7 +1801,7 @@
         <v>75</v>
       </c>
       <c r="M22">
-        <v>0.4876</v>
+        <v>0.4757</v>
       </c>
       <c r="N22">
         <v>1610612752</v>
@@ -1854,7 +1854,7 @@
         <v>76</v>
       </c>
       <c r="M23">
-        <v>0.7046</v>
+        <v>0.7078</v>
       </c>
       <c r="N23">
         <v>1610612752</v>
@@ -1907,7 +1907,7 @@
         <v>75</v>
       </c>
       <c r="M24">
-        <v>0.4876</v>
+        <v>0.4757</v>
       </c>
       <c r="N24">
         <v>1610612752</v>
@@ -1960,7 +1960,7 @@
         <v>76</v>
       </c>
       <c r="M25">
-        <v>0.7046</v>
+        <v>0.7078</v>
       </c>
       <c r="N25">
         <v>1610612752</v>
@@ -2013,7 +2013,7 @@
         <v>78</v>
       </c>
       <c r="M26">
-        <v>0.715</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N26">
         <v>1610612739</v>
@@ -2066,7 +2066,7 @@
         <v>78</v>
       </c>
       <c r="M27">
-        <v>0.715</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N27">
         <v>1610612739</v>
@@ -2119,7 +2119,7 @@
         <v>77</v>
       </c>
       <c r="M28">
-        <v>0.4648</v>
+        <v>0.4487</v>
       </c>
       <c r="N28">
         <v>1610612739</v>
@@ -2172,7 +2172,7 @@
         <v>77</v>
       </c>
       <c r="M29">
-        <v>0.4648</v>
+        <v>0.4487</v>
       </c>
       <c r="N29">
         <v>1610612739</v>
@@ -2225,7 +2225,7 @@
         <v>78</v>
       </c>
       <c r="M30">
-        <v>0.715</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N30">
         <v>1610612739</v>
@@ -2278,7 +2278,7 @@
         <v>77</v>
       </c>
       <c r="M31">
-        <v>0.4648</v>
+        <v>0.4487</v>
       </c>
       <c r="N31">
         <v>1610612739</v>
@@ -2331,7 +2331,7 @@
         <v>78</v>
       </c>
       <c r="M32">
-        <v>0.715</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N32">
         <v>1610612739</v>
@@ -2384,7 +2384,7 @@
         <v>81</v>
       </c>
       <c r="M33">
-        <v>0.5914</v>
+        <v>0.5626</v>
       </c>
       <c r="N33">
         <v>1610612756</v>
@@ -2437,7 +2437,7 @@
         <v>91</v>
       </c>
       <c r="M34">
-        <v>0.6475</v>
+        <v>0.6455</v>
       </c>
       <c r="N34">
         <v>1610612746</v>
@@ -2490,7 +2490,7 @@
         <v>80</v>
       </c>
       <c r="M35">
-        <v>0.5315</v>
+        <v>0.515</v>
       </c>
       <c r="N35">
         <v>1610612757</v>
@@ -2543,7 +2543,7 @@
         <v>81</v>
       </c>
       <c r="M36">
-        <v>0.6456</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="N36">
         <v>1610612760</v>
@@ -2596,7 +2596,7 @@
         <v>81</v>
       </c>
       <c r="M37">
-        <v>0.6456</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="N37">
         <v>1610612760</v>
@@ -2649,7 +2649,7 @@
         <v>82</v>
       </c>
       <c r="M38">
-        <v>0.4232</v>
+        <v>0.2627</v>
       </c>
       <c r="N38">
         <v>1610612760</v>
@@ -2702,7 +2702,7 @@
         <v>82</v>
       </c>
       <c r="M39">
-        <v>0.4232</v>
+        <v>0.2627</v>
       </c>
       <c r="N39">
         <v>1610612760</v>
@@ -2755,7 +2755,7 @@
         <v>81</v>
       </c>
       <c r="M40">
-        <v>0.6456</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="N40">
         <v>1610612760</v>
@@ -2808,7 +2808,7 @@
         <v>82</v>
       </c>
       <c r="M41">
-        <v>0.4232</v>
+        <v>0.2627</v>
       </c>
       <c r="N41">
         <v>1610612760</v>
@@ -2861,7 +2861,7 @@
         <v>81</v>
       </c>
       <c r="M42">
-        <v>0.6456</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="N42">
         <v>1610612760</v>
@@ -2914,7 +2914,7 @@
         <v>79</v>
       </c>
       <c r="M43">
-        <v>0.7333</v>
+        <v>0.7945</v>
       </c>
       <c r="N43">
         <v>1610612759</v>
@@ -2967,7 +2967,7 @@
         <v>79</v>
       </c>
       <c r="M44">
-        <v>0.7333</v>
+        <v>0.7945</v>
       </c>
       <c r="N44">
         <v>1610612759</v>
@@ -3020,7 +3020,7 @@
         <v>83</v>
       </c>
       <c r="M45">
-        <v>0.3895</v>
+        <v>0.3436</v>
       </c>
       <c r="N45">
         <v>1610612759</v>
@@ -3073,7 +3073,7 @@
         <v>83</v>
       </c>
       <c r="M46">
-        <v>0.3895</v>
+        <v>0.3436</v>
       </c>
       <c r="N46">
         <v>1610612759</v>
@@ -3126,7 +3126,7 @@
         <v>79</v>
       </c>
       <c r="M47">
-        <v>0.7333</v>
+        <v>0.7945</v>
       </c>
       <c r="N47">
         <v>1610612759</v>
@@ -3179,7 +3179,7 @@
         <v>83</v>
       </c>
       <c r="M48">
-        <v>0.3895</v>
+        <v>0.3436</v>
       </c>
       <c r="N48">
         <v>1610612759</v>
@@ -3232,7 +3232,7 @@
         <v>79</v>
       </c>
       <c r="M49">
-        <v>0.7333</v>
+        <v>0.7945</v>
       </c>
       <c r="N49">
         <v>1610612759</v>
@@ -3285,7 +3285,7 @@
         <v>85</v>
       </c>
       <c r="M50">
-        <v>0.7055</v>
+        <v>0.6842</v>
       </c>
       <c r="N50">
         <v>1610612743</v>
@@ -3338,7 +3338,7 @@
         <v>85</v>
       </c>
       <c r="M51">
-        <v>0.7055</v>
+        <v>0.6842</v>
       </c>
       <c r="N51">
         <v>1610612743</v>
@@ -3391,7 +3391,7 @@
         <v>84</v>
       </c>
       <c r="M52">
-        <v>0.4217</v>
+        <v>0.4608</v>
       </c>
       <c r="N52">
         <v>1610612743</v>
@@ -3444,7 +3444,7 @@
         <v>84</v>
       </c>
       <c r="M53">
-        <v>0.4217</v>
+        <v>0.4608</v>
       </c>
       <c r="N53">
         <v>1610612743</v>
@@ -3497,7 +3497,7 @@
         <v>85</v>
       </c>
       <c r="M54">
-        <v>0.7055</v>
+        <v>0.6842</v>
       </c>
       <c r="N54">
         <v>1610612743</v>
@@ -3550,7 +3550,7 @@
         <v>84</v>
       </c>
       <c r="M55">
-        <v>0.4217</v>
+        <v>0.4608</v>
       </c>
       <c r="N55">
         <v>1610612743</v>
@@ -3603,7 +3603,7 @@
         <v>85</v>
       </c>
       <c r="M56">
-        <v>0.7055</v>
+        <v>0.6842</v>
       </c>
       <c r="N56">
         <v>1610612743</v>
@@ -3656,7 +3656,7 @@
         <v>87</v>
       </c>
       <c r="M57">
-        <v>0.4704</v>
+        <v>0.4879</v>
       </c>
       <c r="N57">
         <v>1610612747</v>
@@ -3709,7 +3709,7 @@
         <v>87</v>
       </c>
       <c r="M58">
-        <v>0.4704</v>
+        <v>0.4879</v>
       </c>
       <c r="N58">
         <v>1610612747</v>
@@ -3762,7 +3762,7 @@
         <v>86</v>
       </c>
       <c r="M59">
-        <v>0.6264</v>
+        <v>0.6463</v>
       </c>
       <c r="N59">
         <v>1610612747</v>
@@ -3815,7 +3815,7 @@
         <v>86</v>
       </c>
       <c r="M60">
-        <v>0.6264</v>
+        <v>0.6463</v>
       </c>
       <c r="N60">
         <v>1610612747</v>
@@ -3868,7 +3868,7 @@
         <v>87</v>
       </c>
       <c r="M61">
-        <v>0.4704</v>
+        <v>0.4879</v>
       </c>
       <c r="N61">
         <v>1610612747</v>
@@ -3921,7 +3921,7 @@
         <v>86</v>
       </c>
       <c r="M62">
-        <v>0.6264</v>
+        <v>0.6463</v>
       </c>
       <c r="N62">
         <v>1610612747</v>
@@ -3974,7 +3974,7 @@
         <v>87</v>
       </c>
       <c r="M63">
-        <v>0.4704</v>
+        <v>0.4879</v>
       </c>
       <c r="N63">
         <v>1610612747</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -741,7 +741,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>0.5129</v>
+        <v>0.5189</v>
       </c>
       <c r="N2">
         <v>1610612755</v>
@@ -847,7 +847,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>0.5075</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="N4">
         <v>1610612753</v>
@@ -900,7 +900,7 @@
         <v>72</v>
       </c>
       <c r="M5">
-        <v>0.7524999999999999</v>
+        <v>0.7532</v>
       </c>
       <c r="N5">
         <v>1610612765</v>
@@ -953,7 +953,7 @@
         <v>72</v>
       </c>
       <c r="M6">
-        <v>0.7524999999999999</v>
+        <v>0.7532</v>
       </c>
       <c r="N6">
         <v>1610612765</v>
@@ -1006,7 +1006,7 @@
         <v>73</v>
       </c>
       <c r="M7">
-        <v>0.3871</v>
+        <v>0.3961</v>
       </c>
       <c r="N7">
         <v>1610612765</v>
@@ -1059,7 +1059,7 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>0.3871</v>
+        <v>0.3961</v>
       </c>
       <c r="N8">
         <v>1610612765</v>
@@ -1112,7 +1112,7 @@
         <v>72</v>
       </c>
       <c r="M9">
-        <v>0.7524999999999999</v>
+        <v>0.7532</v>
       </c>
       <c r="N9">
         <v>1610612765</v>
@@ -1165,7 +1165,7 @@
         <v>73</v>
       </c>
       <c r="M10">
-        <v>0.3871</v>
+        <v>0.3961</v>
       </c>
       <c r="N10">
         <v>1610612765</v>
@@ -1218,7 +1218,7 @@
         <v>72</v>
       </c>
       <c r="M11">
-        <v>0.7524999999999999</v>
+        <v>0.7532</v>
       </c>
       <c r="N11">
         <v>1610612765</v>
@@ -1271,7 +1271,7 @@
         <v>70</v>
       </c>
       <c r="M12">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="N12">
         <v>1610612738</v>
@@ -1324,7 +1324,7 @@
         <v>70</v>
       </c>
       <c r="M13">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="N13">
         <v>1610612738</v>
@@ -1483,7 +1483,7 @@
         <v>70</v>
       </c>
       <c r="M16">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="N16">
         <v>1610612738</v>
@@ -1589,7 +1589,7 @@
         <v>70</v>
       </c>
       <c r="M18">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="N18">
         <v>1610612738</v>
@@ -2119,7 +2119,7 @@
         <v>77</v>
       </c>
       <c r="M28">
-        <v>0.4487</v>
+        <v>0.4482</v>
       </c>
       <c r="N28">
         <v>1610612739</v>
@@ -2172,7 +2172,7 @@
         <v>77</v>
       </c>
       <c r="M29">
-        <v>0.4487</v>
+        <v>0.4482</v>
       </c>
       <c r="N29">
         <v>1610612739</v>
@@ -2278,7 +2278,7 @@
         <v>77</v>
       </c>
       <c r="M31">
-        <v>0.4487</v>
+        <v>0.4482</v>
       </c>
       <c r="N31">
         <v>1610612739</v>
@@ -2384,7 +2384,7 @@
         <v>81</v>
       </c>
       <c r="M33">
-        <v>0.5626</v>
+        <v>0.5508</v>
       </c>
       <c r="N33">
         <v>1610612756</v>
@@ -2649,7 +2649,7 @@
         <v>82</v>
       </c>
       <c r="M38">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="N38">
         <v>1610612760</v>
@@ -2702,7 +2702,7 @@
         <v>82</v>
       </c>
       <c r="M39">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="N39">
         <v>1610612760</v>
@@ -2808,7 +2808,7 @@
         <v>82</v>
       </c>
       <c r="M41">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="N41">
         <v>1610612760</v>
@@ -2914,7 +2914,7 @@
         <v>79</v>
       </c>
       <c r="M43">
-        <v>0.7945</v>
+        <v>0.8185</v>
       </c>
       <c r="N43">
         <v>1610612759</v>
@@ -2967,7 +2967,7 @@
         <v>79</v>
       </c>
       <c r="M44">
-        <v>0.7945</v>
+        <v>0.8185</v>
       </c>
       <c r="N44">
         <v>1610612759</v>
@@ -3020,7 +3020,7 @@
         <v>83</v>
       </c>
       <c r="M45">
-        <v>0.3436</v>
+        <v>0.3394</v>
       </c>
       <c r="N45">
         <v>1610612759</v>
@@ -3073,7 +3073,7 @@
         <v>83</v>
       </c>
       <c r="M46">
-        <v>0.3436</v>
+        <v>0.3394</v>
       </c>
       <c r="N46">
         <v>1610612759</v>
@@ -3126,7 +3126,7 @@
         <v>79</v>
       </c>
       <c r="M47">
-        <v>0.7945</v>
+        <v>0.8185</v>
       </c>
       <c r="N47">
         <v>1610612759</v>
@@ -3179,7 +3179,7 @@
         <v>83</v>
       </c>
       <c r="M48">
-        <v>0.3436</v>
+        <v>0.3394</v>
       </c>
       <c r="N48">
         <v>1610612759</v>
@@ -3232,7 +3232,7 @@
         <v>79</v>
       </c>
       <c r="M49">
-        <v>0.7945</v>
+        <v>0.8185</v>
       </c>
       <c r="N49">
         <v>1610612759</v>
@@ -3762,7 +3762,7 @@
         <v>86</v>
       </c>
       <c r="M59">
-        <v>0.6463</v>
+        <v>0.6502</v>
       </c>
       <c r="N59">
         <v>1610612747</v>
@@ -3815,7 +3815,7 @@
         <v>86</v>
       </c>
       <c r="M60">
-        <v>0.6463</v>
+        <v>0.6502</v>
       </c>
       <c r="N60">
         <v>1610612747</v>
@@ -3921,7 +3921,7 @@
         <v>86</v>
       </c>
       <c r="M62">
-        <v>0.6463</v>
+        <v>0.6502</v>
       </c>
       <c r="N62">
         <v>1610612747</v>

--- a/nba/public/data/nba_playoff_schedule.xlsx
+++ b/nba/public/data/nba_playoff_schedule.xlsx
@@ -741,7 +741,7 @@
         <v>72</v>
       </c>
       <c r="M2">
-        <v>0.5189</v>
+        <v>0.5619</v>
       </c>
       <c r="N2">
         <v>1610612755</v>
@@ -794,7 +794,7 @@
         <v>90</v>
       </c>
       <c r="M3">
-        <v>0.6605</v>
+        <v>0.6643</v>
       </c>
       <c r="N3">
         <v>1610612766</v>
@@ -847,7 +847,7 @@
         <v>71</v>
       </c>
       <c r="M4">
-        <v>0.5106000000000001</v>
+        <v>0.5134</v>
       </c>
       <c r="N4">
         <v>1610612753</v>
@@ -900,7 +900,7 @@
         <v>72</v>
       </c>
       <c r="M5">
-        <v>0.7532</v>
+        <v>0.728</v>
       </c>
       <c r="N5">
         <v>1610612765</v>
@@ -953,7 +953,7 @@
         <v>72</v>
       </c>
       <c r="M6">
-        <v>0.7532</v>
+        <v>0.728</v>
       </c>
       <c r="N6">
         <v>1610612765</v>
@@ -1006,7 +1006,7 @@
         <v>73</v>
       </c>
       <c r="M7">
-        <v>0.3961</v>
+        <v>0.418</v>
       </c>
       <c r="N7">
         <v>1610612765</v>
@@ -1059,7 +1059,7 @@
         <v>73</v>
       </c>
       <c r="M8">
-        <v>0.3961</v>
+        <v>0.418</v>
       </c>
       <c r="N8">
         <v>1610612765</v>
@@ -1112,7 +1112,7 @@
         <v>72</v>
       </c>
       <c r="M9">
-        <v>0.7532</v>
+        <v>0.728</v>
       </c>
       <c r="N9">
         <v>1610612765</v>
@@ -1165,7 +1165,7 @@
         <v>73</v>
       </c>
       <c r="M10">
-        <v>0.3961</v>
+        <v>0.418</v>
       </c>
       <c r="N10">
         <v>1610612765</v>
@@ -1218,7 +1218,7 @@
         <v>72</v>
       </c>
       <c r="M11">
-        <v>0.7532</v>
+        <v>0.728</v>
       </c>
       <c r="N11">
         <v>1610612765</v>
@@ -1271,7 +1271,7 @@
         <v>70</v>
       </c>
       <c r="M12">
-        <v>0.8129999999999999</v>
+        <v>0.8021</v>
       </c>
       <c r="N12">
         <v>1610612738</v>
@@ -1324,7 +1324,7 @@
         <v>70</v>
       </c>
       <c r="M13">
-        <v>0.8129999999999999</v>
+        <v>0.8021</v>
       </c>
       <c r="N13">
         <v>1610612738</v>
@@ -1377,7 +1377,7 @@
         <v>74</v>
       </c>
       <c r="M14">
-        <v>0.3263</v>
+        <v>0.3381</v>
       </c>
       <c r="N14">
         <v>1610612738</v>
@@ -1430,7 +1430,7 @@
         <v>74</v>
       </c>
       <c r="M15">
-        <v>0.3263</v>
+        <v>0.3381</v>
       </c>
       <c r="N15">
         <v>1610612738</v>
@@ -1483,7 +1483,7 @@
         <v>70</v>
       </c>
       <c r="M16">
-        <v>0.8129999999999999</v>
+        <v>0.8021</v>
       </c>
       <c r="N16">
         <v>1610612738</v>
@@ -1536,7 +1536,7 @@
         <v>74</v>
       </c>
       <c r="M17">
-        <v>0.3263</v>
+        <v>0.3381</v>
       </c>
       <c r="N17">
         <v>1610612738</v>
@@ -1589,7 +1589,7 @@
         <v>70</v>
       </c>
       <c r="M18">
-        <v>0.8129999999999999</v>
+        <v>0.8021</v>
       </c>
       <c r="N18">
         <v>1610612738</v>
@@ -1642,7 +1642,7 @@
         <v>76</v>
       </c>
       <c r="M19">
-        <v>0.7078</v>
+        <v>0.7469</v>
       </c>
       <c r="N19">
         <v>1610612752</v>
@@ -1695,7 +1695,7 @@
         <v>76</v>
       </c>
       <c r="M20">
-        <v>0.7078</v>
+        <v>0.7469</v>
       </c>
       <c r="N20">
         <v>1610612752</v>
@@ -1748,7 +1748,7 @@
         <v>75</v>
       </c>
       <c r="M21">
-        <v>0.4757</v>
+        <v>0.4194</v>
       </c>
       <c r="N21">
         <v>1610612752</v>
@@ -1801,7 +1801,7 @@
         <v>75</v>
       </c>
       <c r="M22">
-        <v>0.4757</v>
+        <v>0.4194</v>
       </c>
       <c r="N22">
         <v>1610612752</v>
@@ -1854,7 +1854,7 @@
         <v>76</v>
       </c>
       <c r="M23">
-        <v>0.7078</v>
+        <v>0.7469</v>
       </c>
       <c r="N23">
         <v>1610612752</v>
@@ -1907,7 +1907,7 @@
         <v>75</v>
       </c>
       <c r="M24">
-        <v>0.4757</v>
+        <v>0.4194</v>
       </c>
       <c r="N24">
         <v>1610612752</v>
@@ -1960,7 +1960,7 @@
         <v>76</v>
       </c>
       <c r="M25">
-        <v>0.7078</v>
+        <v>0.7469</v>
       </c>
       <c r="N25">
         <v>1610612752</v>
@@ -2013,7 +2013,7 @@
         <v>78</v>
       </c>
       <c r="M26">
-        <v>0.6981000000000001</v>
+        <v>0.6876</v>
       </c>
       <c r="N26">
         <v>1610612739</v>
@@ -2066,7 +2066,7 @@
         <v>78</v>
       </c>
       <c r="M27">
-        <v>0.6981000000000001</v>
+        <v>0.6876</v>
       </c>
       <c r="N27">
         <v>1610612739</v>
@@ -2119,7 +2119,7 @@
         <v>77</v>
       </c>
       <c r="M28">
-        <v>0.4482</v>
+        <v>0.4589</v>
       </c>
       <c r="N28">
         <v>1610612739</v>
@@ -2172,7 +2172,7 @@
         <v>77</v>
       </c>
       <c r="M29">
-        <v>0.4482</v>
+        <v>0.4589</v>
       </c>
       <c r="N29">
         <v>1610612739</v>
@@ -2225,7 +2225,7 @@
         <v>78</v>
       </c>
       <c r="M30">
-        <v>0.6981000000000001</v>
+        <v>0.6876</v>
       </c>
       <c r="N30">
         <v>1610612739</v>
@@ -2278,7 +2278,7 @@
         <v>77</v>
       </c>
       <c r="M31">
-        <v>0.4482</v>
+        <v>0.4589</v>
       </c>
       <c r="N31">
         <v>1610612739</v>
@@ -2331,7 +2331,7 @@
         <v>78</v>
       </c>
       <c r="M32">
-        <v>0.6981000000000001</v>
+        <v>0.6876</v>
       </c>
       <c r="N32">
         <v>1610612739</v>
@@ -2384,7 +2384,7 @@
         <v>81</v>
       </c>
       <c r="M33">
-        <v>0.5508</v>
+        <v>0.608</v>
       </c>
       <c r="N33">
         <v>1610612756</v>
@@ -2437,7 +2437,7 @@
         <v>91</v>
       </c>
       <c r="M34">
-        <v>0.6455</v>
+        <v>0.6464</v>
       </c>
       <c r="N34">
         <v>1610612746</v>
@@ -2490,7 +2490,7 @@
         <v>80</v>
       </c>
       <c r="M35">
-        <v>0.515</v>
+        <v>0.4748</v>
       </c>
       <c r="N35">
         <v>1610612757</v>
@@ -2543,7 +2543,7 @@
         <v>81</v>
       </c>
       <c r="M36">
-        <v>0.8038999999999999</v>
+        <v>0.8339</v>
       </c>
       <c r="N36">
         <v>1610612760</v>
@@ -2596,7 +2596,7 @@
         <v>81</v>
       </c>
       <c r="M37">
-        <v>0.8038999999999999</v>
+        <v>0.8339</v>
       </c>
       <c r="N37">
         <v>1610612760</v>
@@ -2649,7 +2649,7 @@
         <v>82</v>
       </c>
       <c r="M38">
-        <v>0.2563</v>
+        <v>0.2431</v>
       </c>
       <c r="N38">
         <v>1610612760</v>
@@ -2702,7 +2702,7 @@
         <v>82</v>
       </c>
       <c r="M39">
-        <v>0.2563</v>
+        <v>0.2431</v>
       </c>
       <c r="N39">
         <v>1610612760</v>
@@ -2755,7 +2755,7 @@
         <v>81</v>
       </c>
       <c r="M40">
-        <v>0.8038999999999999</v>
+        <v>0.8339</v>
       </c>
       <c r="N40">
         <v>1610612760</v>
@@ -2808,7 +2808,7 @@
         <v>82</v>
       </c>
       <c r="M41">
-        <v>0.2563</v>
+        <v>0.2431</v>
       </c>
       <c r="N41">
         <v>1610612760</v>
@@ -2861,7 +2861,7 @@
         <v>81</v>
       </c>
       <c r="M42">
-        <v>0.8038999999999999</v>
+        <v>0.8339</v>
       </c>
       <c r="N42">
         <v>1610612760</v>
@@ -2914,7 +2914,7 @@
         <v>79</v>
       </c>
       <c r="M43">
-        <v>0.8185</v>
+        <v>0.8325</v>
       </c>
       <c r="N43">
         <v>1610612759</v>
@@ -2967,7 +2967,7 @@
         <v>79</v>
       </c>
       <c r="M44">
-        <v>0.8185</v>
+        <v>0.8325</v>
       </c>
       <c r="N44">
         <v>1610612759</v>
@@ -3020,7 +3020,7 @@
         <v>83</v>
       </c>
       <c r="M45">
-        <v>0.3394</v>
+        <v>0.3098</v>
       </c>
       <c r="N45">
         <v>1610612759</v>
@@ -3073,7 +3073,7 @@
         <v>83</v>
       </c>
       <c r="M46">
-        <v>0.3394</v>
+        <v>0.3098</v>
       </c>
       <c r="N46">
         <v>1610612759</v>
@@ -3126,7 +3126,7 @@
         <v>79</v>
       </c>
       <c r="M47">
-        <v>0.8185</v>
+        <v>0.8325</v>
       </c>
       <c r="N47">
         <v>1610612759</v>
@@ -3179,7 +3179,7 @@
         <v>83</v>
       </c>
       <c r="M48">
-        <v>0.3394</v>
+        <v>0.3098</v>
       </c>
       <c r="N48">
         <v>1610612759</v>
@@ -3232,7 +3232,7 @@
         <v>79</v>
       </c>
       <c r="M49">
-        <v>0.8185</v>
+        <v>0.8325</v>
       </c>
       <c r="N49">
         <v>1610612759</v>
@@ -3285,7 +3285,7 @@
         <v>85</v>
       </c>
       <c r="M50">
-        <v>0.6842</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="N50">
         <v>1610612743</v>
@@ -3338,7 +3338,7 @@
         <v>85</v>
       </c>
       <c r="M51">
-        <v>0.6842</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="N51">
         <v>1610612743</v>
@@ -3391,7 +3391,7 @@
         <v>84</v>
       </c>
       <c r="M52">
-        <v>0.4608</v>
+        <v>0.4907</v>
       </c>
       <c r="N52">
         <v>1610612743</v>
@@ -3444,7 +3444,7 @@
         <v>84</v>
       </c>
       <c r="M53">
-        <v>0.4608</v>
+        <v>0.4907</v>
       </c>
       <c r="N53">
         <v>1610612743</v>
@@ -3497,7 +3497,7 @@
         <v>85</v>
       </c>
       <c r="M54">
-        <v>0.6842</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="N54">
         <v>1610612743</v>
@@ -3550,7 +3550,7 @@
         <v>84</v>
       </c>
       <c r="M55">
-        <v>0.4608</v>
+        <v>0.4907</v>
       </c>
       <c r="N55">
         <v>1610612743</v>
@@ -3603,7 +3603,7 @@
         <v>85</v>
       </c>
       <c r="M56">
-        <v>0.6842</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="N56">
         <v>1610612743</v>
@@ -3656,7 +3656,7 @@
         <v>87</v>
       </c>
       <c r="M57">
-        <v>0.4879</v>
+        <v>0.5446</v>
       </c>
       <c r="N57">
         <v>1610612747</v>
@@ -3709,7 +3709,7 @@
         <v>87</v>
       </c>
       <c r="M58">
-        <v>0.4879</v>
+        <v>0.5446</v>
       </c>
       <c r="N58">
         <v>1610612747</v>
@@ -3762,7 +3762,7 @@
         <v>86</v>
       </c>
       <c r="M59">
-        <v>0.6502</v>
+        <v>0.5739</v>
       </c>
       <c r="N59">
         <v>1610612747</v>
@@ -3815,7 +3815,7 @@
         <v>86</v>
       </c>
       <c r="M60">
-        <v>0.6502</v>
+        <v>0.5739</v>
       </c>
       <c r="N60">
         <v>1610612747</v>
@@ -3868,7 +3868,7 @@
         <v>87</v>
       </c>
       <c r="M61">
-        <v>0.4879</v>
+        <v>0.5446</v>
       </c>
       <c r="N61">
         <v>1610612747</v>
@@ -3921,7 +3921,7 @@
         <v>86</v>
       </c>
       <c r="M62">
-        <v>0.6502</v>
+        <v>0.5739</v>
       </c>
       <c r="N62">
         <v>1610612747</v>
@@ -3974,7 +3974,7 @@
         <v>87</v>
       </c>
       <c r="M63">
-        <v>0.4879</v>
+        <v>0.5446</v>
       </c>
       <c r="N63">
         <v>1610612747</v>
